--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 10\Tonor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 11\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021D329D-5E5B-4637-9134-8C1B6A82CE9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DEE87BF-4D24-4627-8A3C-D4CB8761E427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="147">
   <si>
     <t>SKU</t>
   </si>
@@ -75,6 +75,18 @@
     <t>Week</t>
   </si>
   <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Week 11</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1p</t>
+  </si>
+  <si>
     <t>FBA77101</t>
   </si>
   <si>
@@ -240,28 +252,25 @@
     <t>TONOR</t>
   </si>
   <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>Week 10</t>
+    <t>FBA79575</t>
+  </si>
+  <si>
+    <t>FBA79579</t>
+  </si>
+  <si>
+    <t>FBA79578</t>
   </si>
   <si>
     <t>B0BG8CJXHH</t>
   </si>
   <si>
+    <t>B0CQX4GVSB</t>
+  </si>
+  <si>
     <t>B0CFKZ72N7</t>
   </si>
   <si>
-    <t>B0CQX4GVSB</t>
-  </si>
-  <si>
-    <t>Marketplace</t>
-  </si>
-  <si>
-    <t>1p</t>
-  </si>
-  <si>
-    <t>1P</t>
+    <t xml:space="preserve"> Market place</t>
   </si>
   <si>
     <t>Q9</t>
@@ -306,24 +315,15 @@
     <t>K9</t>
   </si>
   <si>
-    <t xml:space="preserve">TD510	</t>
-  </si>
-  <si>
     <t>T90</t>
   </si>
   <si>
-    <t xml:space="preserve">TC310	</t>
-  </si>
-  <si>
     <t>TC310+</t>
   </si>
   <si>
     <t>T10</t>
   </si>
   <si>
-    <t xml:space="preserve">TC777PRO	</t>
-  </si>
-  <si>
     <t>TC30+</t>
   </si>
   <si>
@@ -357,18 +357,12 @@
     <t>TD310+</t>
   </si>
   <si>
-    <t>Tonor</t>
-  </si>
-  <si>
     <t>AMPM</t>
   </si>
   <si>
     <t>Warehouse</t>
   </si>
   <si>
-    <t>B2B - AMPM</t>
-  </si>
-  <si>
     <t>TC310</t>
   </si>
   <si>
@@ -381,28 +375,12 @@
     <t>Dispatch Partner</t>
   </si>
   <si>
+    <t>Open Order</t>
+  </si>
+  <si>
     <t>In-Transit Inventory</t>
   </si>
   <si>
-    <t>Open Order</t>
-  </si>
-  <si>
-    <t>TONORG11</t>
-  </si>
-  <si>
-    <t>TONORTM20</t>
-  </si>
-  <si>
-    <t>TONORTC-2030</t>
-  </si>
-  <si>
-    <t>TONORS20</t>
-  </si>
-  <si>
-    <t>TONOR
-K1</t>
-  </si>
-  <si>
     <t>K1</t>
   </si>
   <si>
@@ -412,42 +390,42 @@
     <t>ORCA001</t>
   </si>
   <si>
+    <t>Condenser Microphone</t>
+  </si>
+  <si>
+    <t>Tripod</t>
+  </si>
+  <si>
+    <t>Dynamic Microphone</t>
+  </si>
+  <si>
+    <t>Hand held Mic</t>
+  </si>
+  <si>
+    <t>USB/XLR Mic</t>
+  </si>
+  <si>
+    <t>Tripod - RGB</t>
+  </si>
+  <si>
+    <t>Hand held Mic + Boom Arm</t>
+  </si>
+  <si>
+    <t>Stand</t>
+  </si>
+  <si>
+    <t>Boom Arm Kit - XLR</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>Boom Arm Kit</t>
+  </si>
+  <si>
     <t>Conference Microphone</t>
   </si>
   <si>
-    <t>Accessories</t>
-  </si>
-  <si>
-    <t>Dynamic Microphone</t>
-  </si>
-  <si>
-    <t>Condenser Microphone</t>
-  </si>
-  <si>
-    <t>Tripod</t>
-  </si>
-  <si>
-    <t>Hand held Mic</t>
-  </si>
-  <si>
-    <t>USB/XLR Mic</t>
-  </si>
-  <si>
-    <t>Tripod - RGB</t>
-  </si>
-  <si>
-    <t>Hand held Mic + Boom Arm</t>
-  </si>
-  <si>
-    <t>Stand</t>
-  </si>
-  <si>
-    <t>Boom Arm Kit - XLR</t>
-  </si>
-  <si>
-    <t>Boom Arm Kit</t>
-  </si>
-  <si>
     <t>Wired</t>
   </si>
   <si>
@@ -478,34 +456,25 @@
     <t>Hand held Mic + Stand</t>
   </si>
   <si>
+    <t>FBA77100</t>
+  </si>
+  <si>
+    <t>B07JMYG6LF</t>
+  </si>
+  <si>
+    <t>FBA77112</t>
+  </si>
+  <si>
+    <t>B083LPYPS9</t>
+  </si>
+  <si>
     <t>Karaoke Machine</t>
   </si>
   <si>
     <t>Portable Speaker with Mic</t>
   </si>
   <si>
-    <t>FBA79575</t>
-  </si>
-  <si>
-    <t>FBA79578</t>
-  </si>
-  <si>
-    <t>FBA79579</t>
-  </si>
-  <si>
-    <t>FBA77100</t>
-  </si>
-  <si>
-    <t>FBA77112</t>
-  </si>
-  <si>
     <t>FBK78924</t>
-  </si>
-  <si>
-    <t>B07JMYG6LF</t>
-  </si>
-  <si>
-    <t>B083LPYPS9</t>
   </si>
   <si>
     <t>B0BGL16PJR</t>
@@ -515,7 +484,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -541,12 +510,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Bookman Old Style"/>
-      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -591,7 +554,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -599,12 +562,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="18" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1017,7 +975,7 @@
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="23.33203125" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="28.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -1069,63 +1027,57 @@
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H2" s="1">
         <v>1206</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H3" s="1">
         <v>1327</v>
@@ -1134,36 +1086,33 @@
         <v>2</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H4" s="1">
         <v>652</v>
@@ -1172,36 +1121,33 @@
         <v>0</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="H5" s="1">
         <v>2412</v>
@@ -1210,36 +1156,33 @@
         <v>0</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H6" s="1">
         <v>1206</v>
@@ -1248,36 +1191,33 @@
         <v>0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>105</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G7" s="1">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="H7" s="1">
         <v>921</v>
@@ -1286,74 +1226,68 @@
         <v>0</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G8" s="1">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H8" s="1">
         <v>1206</v>
       </c>
       <c r="I8">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G9" s="1">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="H9" s="1">
         <v>2412</v>
@@ -1362,36 +1296,33 @@
         <v>4</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G10" s="1">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="H10" s="1">
         <v>3015</v>
@@ -1400,150 +1331,138 @@
         <v>4</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G11" s="1">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="H11" s="1">
         <v>1327</v>
       </c>
       <c r="I11">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G12" s="1">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="H12" s="1">
         <v>1164</v>
       </c>
       <c r="I12">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="H13" s="1">
         <v>1448</v>
       </c>
       <c r="I13">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G14" s="1">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H14" s="1">
         <v>1327</v>
@@ -1552,74 +1471,68 @@
         <v>36</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G15" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H15" s="1">
         <v>652</v>
       </c>
       <c r="I15">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H16" s="1">
         <v>4423</v>
@@ -1628,36 +1541,33 @@
         <v>9</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H17" s="1">
         <v>1930</v>
@@ -1666,36 +1576,33 @@
         <v>5</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G18" s="1">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H18" s="1">
         <v>1930</v>
@@ -1704,36 +1611,33 @@
         <v>23</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B19" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G19" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="H19" s="1">
         <v>1086</v>
@@ -1742,36 +1646,33 @@
         <v>11</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G20" s="1">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="H20" s="1">
         <v>2412</v>
@@ -1780,112 +1681,103 @@
         <v>14</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G21" s="1">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="H21" s="1">
         <v>2412</v>
       </c>
       <c r="I21">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G22" s="1">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H22" s="1">
         <v>1206</v>
       </c>
       <c r="I22">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G23" s="1">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H23" s="1">
         <v>1689</v>
@@ -1894,36 +1786,33 @@
         <v>27</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G24" s="1">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="H24" s="1">
         <v>603</v>
@@ -1932,36 +1821,33 @@
         <v>8</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G25" s="1">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H25" s="1">
         <v>1086</v>
@@ -1970,74 +1856,68 @@
         <v>13</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G26" s="1">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="H26" s="1">
         <v>1280</v>
       </c>
       <c r="I26">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>102</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G27" s="1">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H27" s="1">
         <v>1448</v>
@@ -2046,36 +1926,33 @@
         <v>14</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>96</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="H28" s="1">
         <v>1749</v>
@@ -2084,36 +1961,33 @@
         <v>5</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>97</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G29" s="1">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="H29" s="1">
         <v>965</v>
@@ -2122,36 +1996,33 @@
         <v>63</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>101</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="H30" s="1">
         <v>3491</v>
@@ -2160,36 +2031,33 @@
         <v>3</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>103</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="H31" s="1">
         <v>845</v>
@@ -2198,36 +2066,33 @@
         <v>20</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>100</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="G32" s="1">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="H32" s="1">
         <v>1397</v>
@@ -2236,2486 +2101,2314 @@
         <v>8</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>105</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G33" s="1">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="H33" s="1">
         <v>921</v>
       </c>
       <c r="I33">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C34" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>104</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G34" s="1">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="H34" s="1">
         <v>823</v>
       </c>
       <c r="I34">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G35" s="1">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="H35" s="1">
-        <v>1930</v>
-      </c>
-      <c r="I35">
-        <v>6</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>73</v>
+        <v>921</v>
+      </c>
+      <c r="I35" s="3">
+        <v>44</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G36" s="1">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="H36" s="1">
-        <v>1086</v>
-      </c>
-      <c r="I36">
-        <v>31</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>73</v>
+        <v>2412</v>
+      </c>
+      <c r="I36" s="3">
+        <v>13</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G37" s="1">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H37" s="1">
-        <v>1164</v>
-      </c>
-      <c r="I37">
-        <v>10</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>73</v>
+        <v>1086</v>
+      </c>
+      <c r="I37" s="3">
+        <v>33</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G38" s="1">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H38" s="1">
-        <v>3015</v>
-      </c>
-      <c r="I38"/>
-      <c r="J38" s="3" t="s">
-        <v>73</v>
+        <v>1327</v>
+      </c>
+      <c r="I38" s="3">
+        <v>49</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G39" s="1">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="H39" s="1">
-        <v>1327</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>73</v>
+        <v>1086</v>
+      </c>
+      <c r="I39" s="3">
+        <v>30</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C40" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G40" s="1">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H40" s="1">
-        <v>603</v>
-      </c>
-      <c r="I40">
+        <v>4423</v>
+      </c>
+      <c r="I40" s="3">
         <v>2</v>
       </c>
-      <c r="J40" s="3" t="s">
-        <v>73</v>
+      <c r="J40" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C41" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G41" s="1">
+        <v>129</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1448</v>
+      </c>
+      <c r="I41" s="3">
         <v>0</v>
       </c>
-      <c r="H41" s="1">
-        <v>4423</v>
-      </c>
-      <c r="I41">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>73</v>
+      <c r="J41" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B42" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C42" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>77</v>
+        <v>104</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G42" s="1">
+        <v>138</v>
+      </c>
+      <c r="H42" s="1">
+        <v>823</v>
+      </c>
+      <c r="I42" s="3">
         <v>0</v>
       </c>
-      <c r="H42" s="1">
-        <v>1280</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>73</v>
+      <c r="J42" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>148</v>
+        <v>32</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C43" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G43" s="1">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H43" s="1">
-        <v>1568</v>
-      </c>
-      <c r="I43">
-        <v>10</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>73</v>
+        <v>1689</v>
+      </c>
+      <c r="I43" s="3">
+        <v>8</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C44" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="H44" s="1">
-        <v>2412</v>
-      </c>
-      <c r="I44">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>73</v>
+        <v>1749</v>
+      </c>
+      <c r="I44" s="3">
+        <v>4</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C45" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H45" s="1">
-        <v>2412</v>
-      </c>
-      <c r="I45">
-        <v>6</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>73</v>
+        <v>1930</v>
+      </c>
+      <c r="I45" s="3">
+        <v>10</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C46" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G46" s="1">
-        <v>0</v>
+        <v>127</v>
       </c>
       <c r="H46" s="1">
-        <v>965</v>
-      </c>
-      <c r="I46">
-        <v>7</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>73</v>
+        <v>1164</v>
+      </c>
+      <c r="I46" s="3">
+        <v>9</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B47" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C47" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G47" s="1">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H47" s="1">
-        <v>652</v>
-      </c>
-      <c r="I47">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>73</v>
+        <v>1206</v>
+      </c>
+      <c r="I47" s="3">
+        <v>53</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C48" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G48" s="1">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="H48" s="1">
         <v>1930</v>
       </c>
-      <c r="I48">
-        <v>2</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>73</v>
+      <c r="I48" s="3">
+        <v>5</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>149</v>
+        <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C49" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>126</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G49" s="1">
+        <v>133</v>
+      </c>
+      <c r="H49" s="1">
+        <v>2412</v>
+      </c>
+      <c r="I49" s="3">
         <v>0</v>
       </c>
-      <c r="H49" s="1">
-        <v>1688</v>
-      </c>
-      <c r="I49"/>
-      <c r="J49" s="3" t="s">
-        <v>73</v>
+      <c r="J49" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="C50" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>126</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G50" s="1">
+        <v>127</v>
+      </c>
+      <c r="H50" s="1">
+        <v>1327</v>
+      </c>
+      <c r="I50" s="3">
         <v>0</v>
       </c>
-      <c r="H50" s="1">
-        <v>823</v>
-      </c>
-      <c r="I50">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>73</v>
+      <c r="J50" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="E51" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F51" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F51" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G51" s="1">
-        <v>0</v>
-      </c>
       <c r="H51" s="1">
-        <v>1086</v>
-      </c>
-      <c r="I51">
-        <v>32</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>73</v>
+        <v>603</v>
+      </c>
+      <c r="I51" s="3">
+        <v>2</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>28</v>
+        <v>71</v>
       </c>
       <c r="B52" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="C52" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E52" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G52" s="1">
-        <v>0</v>
-      </c>
       <c r="H52" s="1">
-        <v>1689</v>
-      </c>
-      <c r="I52">
-        <v>11</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>73</v>
+        <v>1568</v>
+      </c>
+      <c r="I52" s="3">
+        <v>9</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C53" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G53" s="1">
+        <v>129</v>
+      </c>
+      <c r="H53" s="1">
+        <v>1280</v>
+      </c>
+      <c r="I53" s="3">
         <v>0</v>
       </c>
-      <c r="H53" s="1">
-        <v>1448</v>
-      </c>
-      <c r="I53">
-        <v>1</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>73</v>
+      <c r="J53" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B54" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C54" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G54" s="1">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="H54" s="1">
-        <v>1749</v>
-      </c>
-      <c r="I54">
-        <v>4</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>73</v>
+        <v>1448</v>
+      </c>
+      <c r="I54" s="3">
+        <v>5</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>150</v>
+        <v>23</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C55" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G55" s="1">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="H55" s="1">
-        <v>1244</v>
-      </c>
-      <c r="I55"/>
-      <c r="J55" s="3" t="s">
-        <v>73</v>
+        <v>3015</v>
+      </c>
+      <c r="I55" t="s">
+        <v>14</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B56" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C56" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G56" s="1">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="H56" s="1">
-        <v>3491</v>
-      </c>
-      <c r="I56"/>
-      <c r="J56" s="3" t="s">
-        <v>73</v>
+        <v>965</v>
+      </c>
+      <c r="I56" s="3">
+        <v>8</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C57" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G57" s="1">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H57" s="1">
-        <v>1448</v>
-      </c>
-      <c r="I57">
-        <v>5</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>73</v>
+        <v>1206</v>
+      </c>
+      <c r="I57" s="3">
+        <v>12</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B58" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C58" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G58" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H58" s="1">
-        <v>1206</v>
-      </c>
-      <c r="I58">
-        <v>12</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>73</v>
+        <v>652</v>
+      </c>
+      <c r="I58" s="3">
+        <v>7</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C59" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H59" s="1">
-        <v>921</v>
-      </c>
-      <c r="I59">
-        <v>42</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>73</v>
+        <v>1244</v>
+      </c>
+      <c r="I59" t="s">
+        <v>14</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B60" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C60" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G60" s="1">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="H60" s="1">
-        <v>1206</v>
-      </c>
-      <c r="I60">
-        <v>58</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>73</v>
+        <v>2412</v>
+      </c>
+      <c r="I60" s="3">
+        <v>3</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="B61" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="C61" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G61" s="1">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H61" s="1">
-        <v>2412</v>
-      </c>
-      <c r="I61">
-        <v>3</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>73</v>
+        <v>1688</v>
+      </c>
+      <c r="I61" t="s">
+        <v>14</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="B62" t="s">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="C62" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G62" s="1">
+        <v>130</v>
+      </c>
+      <c r="H62" s="1">
+        <v>2910</v>
+      </c>
+      <c r="I62" s="1">
         <v>0</v>
       </c>
-      <c r="H62" s="1">
-        <v>1327</v>
-      </c>
-      <c r="I62">
-        <v>51</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>73</v>
+      <c r="J62" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>151</v>
+        <v>16</v>
       </c>
       <c r="B63" t="s">
-        <v>154</v>
-      </c>
-      <c r="C63" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C63" t="s">
+        <v>70</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H63" s="1">
+        <v>1206</v>
+      </c>
+      <c r="I63" s="1">
+        <v>365</v>
+      </c>
+      <c r="J63" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D63" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G63" s="1">
-        <v>0</v>
-      </c>
-      <c r="H63" s="1">
-        <v>2910</v>
-      </c>
-      <c r="I63" s="1">
-        <v>0</v>
-      </c>
-      <c r="J63" s="1" t="s">
+      <c r="K63" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K63" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L63" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="B64" t="s">
-        <v>39</v>
-      </c>
-      <c r="C64" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C64" t="s">
+        <v>70</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H64" s="1">
+        <v>1280</v>
+      </c>
+      <c r="I64" s="1">
+        <v>0</v>
+      </c>
+      <c r="J64" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D64" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G64" s="1">
-        <v>0</v>
-      </c>
-      <c r="H64" s="1">
-        <v>1206</v>
-      </c>
-      <c r="I64" s="1">
-        <v>365</v>
-      </c>
-      <c r="J64" s="1" t="s">
+      <c r="K64" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K64" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L64" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B65" t="s">
-        <v>58</v>
-      </c>
-      <c r="C65" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C65" t="s">
+        <v>70</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H65" s="1">
+        <v>3015</v>
+      </c>
+      <c r="I65" s="1">
+        <v>6</v>
+      </c>
+      <c r="J65" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F65" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G65" s="1">
-        <v>0</v>
-      </c>
-      <c r="H65" s="1">
-        <v>1280</v>
-      </c>
-      <c r="I65" s="1">
-        <v>0</v>
-      </c>
-      <c r="J65" s="1" t="s">
+      <c r="K65" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K65" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L65" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B66" t="s">
-        <v>46</v>
-      </c>
-      <c r="C66" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C66" t="s">
+        <v>70</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1327</v>
+      </c>
+      <c r="I66" s="1">
+        <v>5</v>
+      </c>
+      <c r="J66" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D66" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G66" s="1">
-        <v>0</v>
-      </c>
-      <c r="H66" s="1">
-        <v>3015</v>
-      </c>
-      <c r="I66" s="1">
-        <v>6</v>
-      </c>
-      <c r="J66" s="1" t="s">
+      <c r="K66" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K66" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L66" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>47</v>
-      </c>
-      <c r="C67" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C67" t="s">
+        <v>70</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H67" s="1">
+        <v>1164</v>
+      </c>
+      <c r="I67" s="1">
+        <v>10</v>
+      </c>
+      <c r="J67" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G67" s="1">
-        <v>0</v>
-      </c>
-      <c r="H67" s="1">
-        <v>1327</v>
-      </c>
-      <c r="I67" s="1">
-        <v>5</v>
-      </c>
-      <c r="J67" s="1" t="s">
+      <c r="K67" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K67" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L67" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B68" t="s">
-        <v>48</v>
-      </c>
-      <c r="C68" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C68" t="s">
+        <v>70</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1448</v>
+      </c>
+      <c r="I68" s="1">
+        <v>2</v>
+      </c>
+      <c r="J68" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D68" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F68" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G68" s="1">
-        <v>0</v>
-      </c>
-      <c r="H68" s="1">
-        <v>1164</v>
-      </c>
-      <c r="I68" s="1">
-        <v>10</v>
-      </c>
-      <c r="J68" s="1" t="s">
+      <c r="K68" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K68" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L68" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>49</v>
-      </c>
-      <c r="C69" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C69" t="s">
+        <v>70</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H69" s="1">
+        <v>1327</v>
+      </c>
+      <c r="I69" s="1">
+        <v>285</v>
+      </c>
+      <c r="J69" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G69" s="1">
-        <v>0</v>
-      </c>
-      <c r="H69" s="1">
-        <v>1448</v>
-      </c>
-      <c r="I69" s="1">
-        <v>2</v>
-      </c>
-      <c r="J69" s="1" t="s">
+      <c r="K69" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K69" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L69" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="B70" t="s">
-        <v>40</v>
-      </c>
-      <c r="C70" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C70" t="s">
+        <v>70</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H70" s="1">
+        <v>4423</v>
+      </c>
+      <c r="I70" s="1">
+        <v>0</v>
+      </c>
+      <c r="J70" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D70" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G70" s="1">
-        <v>0</v>
-      </c>
-      <c r="H70" s="1">
-        <v>1327</v>
-      </c>
-      <c r="I70" s="1">
-        <v>287</v>
-      </c>
-      <c r="J70" s="1" t="s">
+      <c r="K70" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K70" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L70" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B71" t="s">
-        <v>50</v>
-      </c>
-      <c r="C71" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C71" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H71" s="1">
+        <v>1930</v>
+      </c>
+      <c r="I71" s="1">
+        <v>13</v>
+      </c>
+      <c r="J71" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D71" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G71" s="1">
-        <v>0</v>
-      </c>
-      <c r="H71" s="1">
-        <v>4423</v>
-      </c>
-      <c r="I71" s="1">
-        <v>0</v>
-      </c>
-      <c r="J71" s="1" t="s">
+      <c r="K71" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K71" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L71" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B72" t="s">
-        <v>51</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>106</v>
+        <v>56</v>
+      </c>
+      <c r="C72" t="s">
+        <v>70</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="G72" s="1">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="H72" s="1">
         <v>1930</v>
       </c>
       <c r="I72" s="1">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="J72" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K72" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K72" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L72" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B73" t="s">
-        <v>52</v>
-      </c>
-      <c r="C73" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" t="s">
+        <v>70</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H73" s="1">
+        <v>1086</v>
+      </c>
+      <c r="I73" s="1">
+        <v>12</v>
+      </c>
+      <c r="J73" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D73" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G73" s="1">
-        <v>0</v>
-      </c>
-      <c r="H73" s="1">
-        <v>1930</v>
-      </c>
-      <c r="I73" s="1">
-        <v>52</v>
-      </c>
-      <c r="J73" s="1" t="s">
+      <c r="K73" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K73" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L73" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B74" t="s">
-        <v>53</v>
-      </c>
-      <c r="C74" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" t="s">
+        <v>70</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H74" s="1">
+        <v>652</v>
+      </c>
+      <c r="I74" s="1">
+        <v>6</v>
+      </c>
+      <c r="J74" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D74" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F74" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="G74" s="1">
-        <v>0</v>
-      </c>
-      <c r="H74" s="1">
-        <v>1086</v>
-      </c>
-      <c r="I74" s="1">
-        <v>12</v>
-      </c>
-      <c r="J74" s="1" t="s">
+      <c r="K74" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K74" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L74" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B75" t="s">
-        <v>41</v>
-      </c>
-      <c r="C75" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C75" t="s">
+        <v>70</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H75" s="1">
+        <v>2412</v>
+      </c>
+      <c r="I75" s="1">
+        <v>10</v>
+      </c>
+      <c r="J75" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D75" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G75" s="1">
-        <v>0</v>
-      </c>
-      <c r="H75" s="1">
-        <v>652</v>
-      </c>
-      <c r="I75" s="1">
-        <v>6</v>
-      </c>
-      <c r="J75" s="1" t="s">
+      <c r="K75" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K75" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L75" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>18</v>
+        <v>141</v>
       </c>
       <c r="B76" t="s">
-        <v>45</v>
-      </c>
-      <c r="C76" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C76" t="s">
+        <v>70</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H76" s="1">
+        <v>12803</v>
+      </c>
+      <c r="I76" s="1">
+        <v>0</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D76" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="G76" s="1">
-        <v>0</v>
-      </c>
-      <c r="H76" s="1">
-        <v>2412</v>
-      </c>
-      <c r="I76" s="1">
-        <v>10</v>
-      </c>
-      <c r="J76" s="1" t="s">
+      <c r="K76" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K76" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L76" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B77" t="s">
-        <v>155</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>106</v>
+        <v>146</v>
+      </c>
+      <c r="C77" t="s">
+        <v>70</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G77" s="1">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="H77" s="1">
-        <v>12803</v>
+        <v>6983</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
       </c>
       <c r="J77" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K77" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K77" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L77" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>153</v>
+        <v>19</v>
       </c>
       <c r="B78" t="s">
-        <v>156</v>
-      </c>
-      <c r="C78" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C78" t="s">
+        <v>70</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H78" s="1">
+        <v>2412</v>
+      </c>
+      <c r="I78" s="1">
+        <v>12</v>
+      </c>
+      <c r="J78" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="G78" s="1">
+      <c r="K78" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="L78" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>31</v>
+      </c>
+      <c r="B79" t="s">
+        <v>58</v>
+      </c>
+      <c r="C79" t="s">
+        <v>70</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H79" s="1">
+        <v>2412</v>
+      </c>
+      <c r="I79" s="1">
         <v>0</v>
       </c>
-      <c r="H78" s="1">
-        <v>6983</v>
-      </c>
-      <c r="I78" s="1">
-        <v>0</v>
-      </c>
-      <c r="J78" s="1" t="s">
+      <c r="J79" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K79" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K78" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L78" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E79" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H79" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I79" s="1">
-        <v>13</v>
-      </c>
-      <c r="J79" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L79" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B80" t="s">
-        <v>54</v>
-      </c>
-      <c r="C80" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C80" t="s">
+        <v>70</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H80" s="1">
+        <v>1206</v>
+      </c>
+      <c r="I80" s="1">
+        <v>5</v>
+      </c>
+      <c r="J80" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D80" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G80" s="1">
-        <v>0</v>
-      </c>
-      <c r="H80" s="1">
-        <v>2412</v>
-      </c>
-      <c r="I80" s="1">
-        <v>0</v>
-      </c>
-      <c r="J80" s="1" t="s">
+      <c r="K80" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K80" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L80" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B81" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C81" s="4" t="s">
+      <c r="A81" t="s">
+        <v>32</v>
+      </c>
+      <c r="B81" t="s">
+        <v>59</v>
+      </c>
+      <c r="C81" t="s">
+        <v>70</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H81" s="1">
+        <v>1689</v>
+      </c>
+      <c r="I81" s="1">
+        <v>188</v>
+      </c>
+      <c r="J81" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D81" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E81" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H81" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I81" s="1">
-        <v>5</v>
-      </c>
-      <c r="J81" s="1" t="s">
+      <c r="K81" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K81" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L81" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B82" t="s">
-        <v>55</v>
-      </c>
-      <c r="C82" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C82" t="s">
+        <v>70</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H82" s="1">
+        <v>603</v>
+      </c>
+      <c r="I82" s="1">
+        <v>2</v>
+      </c>
+      <c r="J82" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G82" s="1">
-        <v>0</v>
-      </c>
-      <c r="H82" s="1">
-        <v>1689</v>
-      </c>
-      <c r="I82" s="1">
-        <v>188</v>
-      </c>
-      <c r="J82" s="1" t="s">
+      <c r="K82" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K82" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L82" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B83" t="s">
-        <v>56</v>
-      </c>
-      <c r="C83" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C83" t="s">
+        <v>70</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H83" s="1">
+        <v>1086</v>
+      </c>
+      <c r="I83" s="1">
+        <v>418</v>
+      </c>
+      <c r="J83" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G83" s="1">
+      <c r="K83" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>71</v>
+      </c>
+      <c r="B84" t="s">
+        <v>74</v>
+      </c>
+      <c r="C84" t="s">
+        <v>70</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H84" s="1">
+        <v>1568</v>
+      </c>
+      <c r="I84" s="1">
         <v>0</v>
       </c>
-      <c r="H83" s="1">
-        <v>603</v>
-      </c>
-      <c r="I83" s="1">
-        <v>2</v>
-      </c>
-      <c r="J83" s="1" t="s">
+      <c r="J84" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K84" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K83" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="L83" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B84" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E84" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H84" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I84" s="1">
-        <v>420</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L84" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>148</v>
+        <v>37</v>
       </c>
       <c r="B85" t="s">
-        <v>69</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>106</v>
+        <v>64</v>
+      </c>
+      <c r="C85" t="s">
+        <v>70</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G85" s="1">
-        <v>0</v>
-      </c>
       <c r="H85" s="1">
-        <v>1568</v>
+        <v>1749</v>
       </c>
       <c r="I85" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J85" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K85" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K85" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L85" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B86" t="s">
-        <v>60</v>
-      </c>
-      <c r="C86" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C86" t="s">
+        <v>70</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H86" s="1">
+        <v>965</v>
+      </c>
+      <c r="I86" s="1">
+        <v>20</v>
+      </c>
+      <c r="J86" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="G86" s="1">
-        <v>0</v>
-      </c>
-      <c r="H86" s="1">
-        <v>1749</v>
-      </c>
-      <c r="I86" s="1">
-        <v>10</v>
-      </c>
-      <c r="J86" s="1" t="s">
+      <c r="K86" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K86" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L86" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="B87" t="s">
-        <v>61</v>
-      </c>
-      <c r="C87" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C87" t="s">
+        <v>70</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H87" s="1">
+        <v>1688</v>
+      </c>
+      <c r="I87" s="1">
+        <v>2</v>
+      </c>
+      <c r="J87" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G87" s="1">
-        <v>0</v>
-      </c>
-      <c r="H87" s="1">
-        <v>965</v>
-      </c>
-      <c r="I87" s="1">
-        <v>20</v>
-      </c>
-      <c r="J87" s="1" t="s">
+      <c r="K87" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K87" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L87" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>149</v>
+        <v>72</v>
       </c>
       <c r="B88" t="s">
-        <v>70</v>
-      </c>
-      <c r="C88" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C88" t="s">
+        <v>70</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H88" s="1">
+        <v>1244</v>
+      </c>
+      <c r="I88" s="1">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G88" s="1">
-        <v>0</v>
-      </c>
-      <c r="H88" s="1">
-        <v>1688</v>
-      </c>
-      <c r="I88" s="1">
-        <v>2</v>
-      </c>
-      <c r="J88" s="1" t="s">
+      <c r="K88" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K88" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L88" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>150</v>
+        <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>106</v>
+        <v>68</v>
+      </c>
+      <c r="C89" t="s">
+        <v>70</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>126</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="G89" s="1">
-        <v>0</v>
+        <v>137</v>
       </c>
       <c r="H89" s="1">
-        <v>1244</v>
+        <v>1397</v>
       </c>
       <c r="I89" s="1">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J89" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K89" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K89" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L89" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B90" t="s">
-        <v>64</v>
-      </c>
-      <c r="C90" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C90" t="s">
+        <v>70</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H90" s="1">
+        <v>3491</v>
+      </c>
+      <c r="I90" s="1">
+        <v>2</v>
+      </c>
+      <c r="J90" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="G90" s="1">
-        <v>0</v>
-      </c>
-      <c r="H90" s="1">
-        <v>1397</v>
-      </c>
-      <c r="I90" s="1">
-        <v>8</v>
-      </c>
-      <c r="J90" s="1" t="s">
+      <c r="K90" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K90" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L90" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B91" t="s">
-        <v>62</v>
-      </c>
-      <c r="C91" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C91" t="s">
+        <v>70</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H91" s="1">
+        <v>1448</v>
+      </c>
+      <c r="I91" s="1">
+        <v>31</v>
+      </c>
+      <c r="J91" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F91" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G91" s="1">
-        <v>0</v>
-      </c>
-      <c r="H91" s="1">
-        <v>3491</v>
-      </c>
-      <c r="I91" s="1">
-        <v>2</v>
-      </c>
-      <c r="J91" s="1" t="s">
+      <c r="K91" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K91" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L91" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B92" t="s">
-        <v>59</v>
-      </c>
-      <c r="C92" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C92" t="s">
+        <v>70</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="H92" s="1">
+        <v>845</v>
+      </c>
+      <c r="I92" s="1">
+        <v>49</v>
+      </c>
+      <c r="J92" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F92" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G92" s="1">
-        <v>0</v>
-      </c>
-      <c r="H92" s="1">
-        <v>1448</v>
-      </c>
-      <c r="I92" s="1">
-        <v>31</v>
-      </c>
-      <c r="J92" s="1" t="s">
+      <c r="K92" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K92" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L92" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="B93" t="s">
-        <v>63</v>
-      </c>
-      <c r="C93" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C93" t="s">
+        <v>70</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H93" s="1">
+        <v>823</v>
+      </c>
+      <c r="I93" s="1">
+        <v>1</v>
+      </c>
+      <c r="J93" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F93" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="G93" s="1">
-        <v>0</v>
-      </c>
-      <c r="H93" s="1">
-        <v>845</v>
-      </c>
-      <c r="I93" s="1">
-        <v>49</v>
-      </c>
-      <c r="J93" s="1" t="s">
+      <c r="K93" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K93" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L93" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B94" t="s">
-        <v>65</v>
-      </c>
-      <c r="C94" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C94" t="s">
+        <v>70</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H94" s="1">
+        <v>921</v>
+      </c>
+      <c r="I94" s="1">
+        <v>110</v>
+      </c>
+      <c r="J94" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F94" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G94" s="1">
-        <v>0</v>
-      </c>
-      <c r="H94" s="1">
-        <v>823</v>
-      </c>
-      <c r="I94" s="1">
-        <v>0</v>
-      </c>
-      <c r="J94" s="1" t="s">
+      <c r="K94" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K94" s="1" t="s">
-        <v>108</v>
-      </c>
       <c r="L94" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B95" t="s">
-        <v>44</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>106</v>
+        <v>43</v>
+      </c>
+      <c r="C95" t="s">
+        <v>70</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="G95" s="1">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="H95" s="1">
-        <v>921</v>
+        <v>1206</v>
       </c>
       <c r="I95" s="1">
-        <v>129</v>
+        <v>2</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B96" t="s">
-        <v>43</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>106</v>
+        <v>47</v>
+      </c>
+      <c r="C96" t="s">
+        <v>70</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G96" s="1">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H96" s="1">
         <v>1206</v>
       </c>
       <c r="I96" s="1">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B97" t="s">
-        <v>39</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>106</v>
+        <v>61</v>
+      </c>
+      <c r="C97" t="s">
+        <v>70</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="G97" s="1">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="H97" s="1">
-        <v>1206</v>
+        <v>1086</v>
       </c>
       <c r="I97" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="B98" t="s">
-        <v>43</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>106</v>
+        <v>62</v>
+      </c>
+      <c r="C98" t="s">
+        <v>70</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G98" s="1">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="H98" s="1">
-        <v>1206</v>
+        <v>1280</v>
       </c>
       <c r="I98" s="1">
-        <v>3</v>
+        <v>240</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>112</v>
@@ -4724,36 +4417,33 @@
         <v>113</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
+        <v>24</v>
+      </c>
+      <c r="B99" t="s">
+        <v>51</v>
+      </c>
+      <c r="C99" t="s">
+        <v>70</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H99" s="1">
+        <v>1327</v>
+      </c>
+      <c r="I99" s="1">
         <v>30</v>
-      </c>
-      <c r="B99" t="s">
-        <v>57</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="G99" s="1">
-        <v>0</v>
-      </c>
-      <c r="H99" s="1">
-        <v>1086</v>
-      </c>
-      <c r="I99" s="1">
-        <v>4</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>112</v>
@@ -4762,205 +4452,217 @@
         <v>113</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B100" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>66</v>
+      <c r="A100" t="s">
+        <v>26</v>
+      </c>
+      <c r="B100" t="s">
+        <v>53</v>
+      </c>
+      <c r="C100" t="s">
+        <v>70</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E100" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H100" s="1" t="e">
-        <v>#N/A</v>
+        <v>84</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H100" s="1">
+        <v>1448</v>
       </c>
       <c r="I100" s="1">
-        <v>240</v>
+        <v>150</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K100" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L100" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>27</v>
+      </c>
+      <c r="B101" t="s">
+        <v>54</v>
+      </c>
+      <c r="C101" t="s">
+        <v>70</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H101" s="1">
+        <v>4423</v>
+      </c>
+      <c r="I101" s="1">
+        <v>80</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>30</v>
+      </c>
+      <c r="B102" t="s">
+        <v>57</v>
+      </c>
+      <c r="C102" t="s">
+        <v>70</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H102" s="1">
+        <v>1086</v>
+      </c>
+      <c r="I102" s="1">
+        <v>204</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>18</v>
+      </c>
+      <c r="B103" t="s">
+        <v>45</v>
+      </c>
+      <c r="C103" t="s">
+        <v>70</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="L100" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B101" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="E101" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H101" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I101" s="1">
-        <v>150</v>
-      </c>
-      <c r="J101" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="L101" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B102" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="E102" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H102" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I102" s="1">
-        <v>80</v>
-      </c>
-      <c r="J102" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="L102" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B103" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D103" s="1" t="s">
+      <c r="E103" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E103" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H103" s="1" t="e">
-        <v>#N/A</v>
+      <c r="F103" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H103" s="1">
+        <v>652</v>
       </c>
       <c r="I103" s="1">
-        <v>204</v>
+        <v>1026</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K103" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="B104" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>66</v>
+      <c r="A104" t="s">
+        <v>42</v>
+      </c>
+      <c r="B104" t="s">
+        <v>69</v>
+      </c>
+      <c r="C104" t="s">
+        <v>70</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E104" s="1" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H104" s="1" t="e">
-        <v>#N/A</v>
+        <v>104</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H104" s="1">
+        <v>823</v>
       </c>
       <c r="I104" s="1">
-        <v>1026</v>
+        <v>504</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K104" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B105" t="s">
-        <v>65</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>66</v>
+        <v>48</v>
+      </c>
+      <c r="C105" t="s">
+        <v>70</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="G105" s="1">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="H105" s="1">
-        <v>823</v>
+        <v>921</v>
       </c>
       <c r="I105" s="1">
-        <v>504</v>
+        <v>256</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 14\Tonor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A54884E8-022F-4150-8BD3-C3D9F3C51D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CC5384-BEFC-49CC-A658-BD32D50925B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -174,9 +174,6 @@
     <t>B0CFKZ72N7</t>
   </si>
   <si>
-    <t>Ampm</t>
-  </si>
-  <si>
     <t>Warehouse</t>
   </si>
   <si>
@@ -496,6 +493,9 @@
   </si>
   <si>
     <t>YNT</t>
+  </si>
+  <si>
+    <t>AMPM</t>
   </si>
 </sst>
 </file>
@@ -1227,22 +1227,22 @@
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>17</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5">
@@ -1252,10 +1252,10 @@
         <v>7</v>
       </c>
       <c r="J2" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L2" s="5" t="s">
         <v>14</v>
@@ -1263,22 +1263,22 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>17</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5">
@@ -1288,10 +1288,10 @@
         <v>1026</v>
       </c>
       <c r="J3" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K3" s="13" t="s">
         <v>120</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>121</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>14</v>
@@ -1299,22 +1299,22 @@
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>19</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5">
@@ -1324,10 +1324,10 @@
         <v>10</v>
       </c>
       <c r="J4" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>14</v>
@@ -1335,22 +1335,22 @@
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G5" s="5">
         <v>0</v>
@@ -1360,10 +1360,10 @@
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>14</v>
@@ -1371,22 +1371,22 @@
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
@@ -1396,10 +1396,10 @@
         <v>0</v>
       </c>
       <c r="J6" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K6" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>14</v>
@@ -1407,22 +1407,22 @@
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>44</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
@@ -1432,10 +1432,10 @@
       </c>
       <c r="I7" s="5"/>
       <c r="J7" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>14</v>
@@ -1443,22 +1443,22 @@
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
@@ -1468,10 +1468,10 @@
         <v>2</v>
       </c>
       <c r="J8" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>14</v>
@@ -1479,22 +1479,22 @@
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5">
@@ -1515,22 +1515,22 @@
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
@@ -1540,10 +1540,10 @@
         <v>0</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>14</v>
@@ -1551,22 +1551,22 @@
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>33</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
@@ -1576,10 +1576,10 @@
         <v>0</v>
       </c>
       <c r="J11" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>14</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
@@ -1612,10 +1612,10 @@
         <v>240</v>
       </c>
       <c r="J12" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K12" s="13" t="s">
         <v>120</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>121</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>14</v>
@@ -1623,22 +1623,22 @@
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5">
@@ -1659,22 +1659,22 @@
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
@@ -1695,22 +1695,22 @@
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>17</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
@@ -1720,10 +1720,10 @@
         <v>3</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>14</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>63</v>
-      </c>
       <c r="C16" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>138</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5">
@@ -1756,10 +1756,10 @@
         <v>0</v>
       </c>
       <c r="J16" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K16" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>14</v>
@@ -1767,16 +1767,16 @@
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>65</v>
-      </c>
       <c r="C17" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E17" s="5" t="e">
         <v>#N/A</v>
@@ -1790,10 +1790,10 @@
         <v>0</v>
       </c>
       <c r="J17" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K17" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>14</v>
@@ -1801,22 +1801,22 @@
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
@@ -1837,22 +1837,22 @@
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>19</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
@@ -1862,10 +1862,10 @@
         <v>2</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>14</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="C20" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>84</v>
-      </c>
       <c r="E20" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5">
@@ -1898,10 +1898,10 @@
         <v>0</v>
       </c>
       <c r="J20" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K20" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K20" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>14</v>
@@ -1909,22 +1909,22 @@
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
@@ -1945,22 +1945,22 @@
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5">
@@ -1970,10 +1970,10 @@
         <v>27</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>14</v>
@@ -1981,22 +1981,22 @@
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
@@ -2006,10 +2006,10 @@
         <v>5</v>
       </c>
       <c r="J23" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K23" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>14</v>
@@ -2017,22 +2017,22 @@
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5">
@@ -2042,10 +2042,10 @@
         <v>204</v>
       </c>
       <c r="J24" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K24" s="13" t="s">
         <v>120</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>121</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>14</v>
@@ -2053,22 +2053,22 @@
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5">
@@ -2089,22 +2089,22 @@
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5">
@@ -2114,10 +2114,10 @@
         <v>2</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L26" s="5" t="s">
         <v>14</v>
@@ -2125,22 +2125,22 @@
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5">
@@ -2150,10 +2150,10 @@
         <v>3</v>
       </c>
       <c r="J27" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K27" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L27" s="5" t="s">
         <v>14</v>
@@ -2161,22 +2161,22 @@
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5">
@@ -2197,22 +2197,22 @@
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5">
@@ -2222,10 +2222,10 @@
         <v>5</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>14</v>
@@ -2233,22 +2233,22 @@
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5">
@@ -2258,10 +2258,10 @@
         <v>11</v>
       </c>
       <c r="J30" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K30" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>14</v>
@@ -2269,22 +2269,22 @@
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5">
@@ -2305,22 +2305,22 @@
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>38</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5">
@@ -2330,10 +2330,10 @@
         <v>48</v>
       </c>
       <c r="J32" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K32" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>14</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5">
@@ -2377,22 +2377,22 @@
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>21</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G34" s="5">
         <v>0</v>
@@ -2402,10 +2402,10 @@
       </c>
       <c r="I34" s="5"/>
       <c r="J34" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>14</v>
@@ -2413,22 +2413,22 @@
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>21</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5">
@@ -2438,10 +2438,10 @@
         <v>5</v>
       </c>
       <c r="J35" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K35" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L35" s="5" t="s">
         <v>14</v>
@@ -2449,22 +2449,22 @@
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>21</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5">
@@ -2474,10 +2474,10 @@
         <v>30</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K36" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>14</v>
@@ -2485,22 +2485,22 @@
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5">
@@ -2521,22 +2521,22 @@
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>28</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G38" s="5">
         <v>0</v>
@@ -2546,10 +2546,10 @@
       </c>
       <c r="I38" s="5"/>
       <c r="J38" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>14</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5">
@@ -2582,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="J39" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K39" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K39" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>14</v>
@@ -2593,22 +2593,22 @@
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5">
@@ -2629,22 +2629,22 @@
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>20</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G41" s="5">
         <v>0</v>
@@ -2654,10 +2654,10 @@
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L41" s="5" t="s">
         <v>14</v>
@@ -2665,22 +2665,22 @@
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>20</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5">
@@ -2690,10 +2690,10 @@
         <v>6</v>
       </c>
       <c r="J42" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K42" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K42" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L42" s="5" t="s">
         <v>14</v>
@@ -2701,22 +2701,22 @@
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E43" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5">
@@ -2737,22 +2737,22 @@
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E44" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F44" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5">
@@ -2762,10 +2762,10 @@
         <v>2</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>14</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B45" s="8" t="s">
         <v>24</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E45" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F45" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5">
@@ -2798,10 +2798,10 @@
         <v>0</v>
       </c>
       <c r="J45" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K45" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K45" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L45" s="5" t="s">
         <v>14</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>24</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E46" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F46" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5">
@@ -2834,10 +2834,10 @@
         <v>80</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K46" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L46" s="5" t="s">
         <v>14</v>
@@ -2845,22 +2845,22 @@
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5">
@@ -2881,22 +2881,22 @@
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5">
@@ -2917,22 +2917,22 @@
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5">
@@ -2942,10 +2942,10 @@
         <v>38</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L49" s="5" t="s">
         <v>14</v>
@@ -2953,22 +2953,22 @@
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5">
@@ -2978,10 +2978,10 @@
         <v>279</v>
       </c>
       <c r="J50" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K50" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K50" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L50" s="5" t="s">
         <v>14</v>
@@ -2989,22 +2989,22 @@
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5">
@@ -3014,10 +3014,10 @@
         <v>9</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L51" s="5" t="s">
         <v>14</v>
@@ -3025,22 +3025,22 @@
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>43</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5">
@@ -3050,10 +3050,10 @@
         <v>0</v>
       </c>
       <c r="J52" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K52" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K52" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L52" s="5" t="s">
         <v>14</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5">
@@ -3097,22 +3097,22 @@
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>34</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5">
@@ -3122,10 +3122,10 @@
         <v>4</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>14</v>
@@ -3133,22 +3133,22 @@
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5">
@@ -3158,10 +3158,10 @@
         <v>31</v>
       </c>
       <c r="J55" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K55" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K55" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L55" s="5" t="s">
         <v>14</v>
@@ -3169,22 +3169,22 @@
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5">
@@ -3205,22 +3205,22 @@
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>35</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5">
@@ -3230,10 +3230,10 @@
         <v>4</v>
       </c>
       <c r="J57" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L57" s="5" t="s">
         <v>14</v>
@@ -3241,22 +3241,22 @@
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5">
@@ -3266,10 +3266,10 @@
         <v>10</v>
       </c>
       <c r="J58" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K58" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K58" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L58" s="5" t="s">
         <v>14</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5">
@@ -3313,22 +3313,22 @@
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5">
@@ -3338,10 +3338,10 @@
         <v>6</v>
       </c>
       <c r="J60" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L60" s="5" t="s">
         <v>14</v>
@@ -3349,22 +3349,22 @@
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>29</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5">
@@ -3374,10 +3374,10 @@
         <v>20</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K61" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L61" s="5" t="s">
         <v>14</v>
@@ -3385,22 +3385,22 @@
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5">
@@ -3410,10 +3410,10 @@
         <v>3</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K62" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L62" s="5" t="s">
         <v>14</v>
@@ -3421,22 +3421,22 @@
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>29</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5">
@@ -3446,10 +3446,10 @@
         <v>5</v>
       </c>
       <c r="J63" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K63" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K63" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L63" s="5" t="s">
         <v>14</v>
@@ -3457,22 +3457,22 @@
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5">
@@ -3493,22 +3493,22 @@
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5">
@@ -3518,10 +3518,10 @@
         <v>7</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L65" s="5" t="s">
         <v>14</v>
@@ -3529,22 +3529,22 @@
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>30</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5">
@@ -3554,10 +3554,10 @@
         <v>188</v>
       </c>
       <c r="J66" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K66" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K66" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L66" s="5" t="s">
         <v>14</v>
@@ -3565,22 +3565,22 @@
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E67" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F67" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5">
@@ -3601,22 +3601,22 @@
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E68" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F68" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5">
@@ -3626,10 +3626,10 @@
         <v>3</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L68" s="5" t="s">
         <v>14</v>
@@ -3637,22 +3637,22 @@
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B69" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E69" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F69" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="F69" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5">
@@ -3662,10 +3662,10 @@
         <v>13</v>
       </c>
       <c r="J69" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K69" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K69" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L69" s="5" t="s">
         <v>14</v>
@@ -3673,22 +3673,22 @@
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5">
@@ -3709,22 +3709,22 @@
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5">
@@ -3734,10 +3734,10 @@
         <v>9</v>
       </c>
       <c r="J71" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L71" s="5" t="s">
         <v>14</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5">
@@ -3770,10 +3770,10 @@
         <v>52</v>
       </c>
       <c r="J72" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K72" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K72" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L72" s="5" t="s">
         <v>14</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5">
@@ -3817,22 +3817,22 @@
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5">
@@ -3853,22 +3853,22 @@
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5">
@@ -3878,10 +3878,10 @@
         <v>42</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L75" s="5" t="s">
         <v>14</v>
@@ -3889,22 +3889,22 @@
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5">
@@ -3914,10 +3914,10 @@
         <v>359</v>
       </c>
       <c r="J76" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K76" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K76" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L76" s="5" t="s">
         <v>14</v>
@@ -3925,22 +3925,22 @@
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5">
@@ -3950,10 +3950,10 @@
         <v>2</v>
       </c>
       <c r="J77" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K77" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L77" s="5" t="s">
         <v>14</v>
@@ -3961,22 +3961,22 @@
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5">
@@ -3986,10 +3986,10 @@
         <v>30</v>
       </c>
       <c r="J78" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K78" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L78" s="5" t="s">
         <v>14</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5">
@@ -4033,22 +4033,22 @@
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5">
@@ -4058,10 +4058,10 @@
         <v>14</v>
       </c>
       <c r="J80" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L80" s="5" t="s">
         <v>14</v>
@@ -4069,22 +4069,22 @@
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>32</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5">
@@ -4094,10 +4094,10 @@
         <v>4</v>
       </c>
       <c r="J81" s="12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K81" s="14" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L81" s="5" t="s">
         <v>14</v>
@@ -4105,22 +4105,22 @@
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5">
@@ -4130,10 +4130,10 @@
         <v>379</v>
       </c>
       <c r="J82" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K82" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K82" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L82" s="5" t="s">
         <v>14</v>
@@ -4141,22 +4141,22 @@
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="5">
@@ -4177,22 +4177,22 @@
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G84" s="5"/>
       <c r="H84" s="5">
@@ -4202,10 +4202,10 @@
         <v>0</v>
       </c>
       <c r="J84" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L84" s="5" t="s">
         <v>14</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>41</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5">
@@ -4238,10 +4238,10 @@
         <v>1</v>
       </c>
       <c r="J85" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K85" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K85" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L85" s="5" t="s">
         <v>14</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>41</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5">
@@ -4274,10 +4274,10 @@
         <v>504</v>
       </c>
       <c r="J86" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K86" s="13" t="s">
         <v>120</v>
-      </c>
-      <c r="K86" s="13" t="s">
-        <v>121</v>
       </c>
       <c r="L86" s="5" t="s">
         <v>14</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5">
@@ -4321,22 +4321,22 @@
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>40</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5">
@@ -4346,10 +4346,10 @@
         <v>44</v>
       </c>
       <c r="J88" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L88" s="5" t="s">
         <v>14</v>
@@ -4357,22 +4357,22 @@
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5">
@@ -4382,10 +4382,10 @@
         <v>100</v>
       </c>
       <c r="J89" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K89" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K89" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L89" s="5" t="s">
         <v>14</v>
@@ -4393,22 +4393,22 @@
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="5">
@@ -4418,10 +4418,10 @@
         <v>256</v>
       </c>
       <c r="J90" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K90" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="L90" s="5" t="s">
         <v>14</v>
@@ -4429,22 +4429,22 @@
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="5">
@@ -4465,22 +4465,22 @@
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5">
@@ -4501,22 +4501,22 @@
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>18</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5">
@@ -4526,10 +4526,10 @@
         <v>7</v>
       </c>
       <c r="J93" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L93" s="5" t="s">
         <v>14</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B94" s="8" t="s">
         <v>18</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="5">
@@ -4562,10 +4562,10 @@
         <v>11</v>
       </c>
       <c r="J94" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K94" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K94" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L94" s="5" t="s">
         <v>14</v>
@@ -4573,22 +4573,22 @@
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G95" s="5"/>
       <c r="H95" s="5">
@@ -4609,22 +4609,22 @@
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>37</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G96" s="5">
         <v>0</v>
@@ -4634,10 +4634,10 @@
       </c>
       <c r="I96" s="5"/>
       <c r="J96" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L96" s="5" t="s">
         <v>14</v>
@@ -4645,22 +4645,22 @@
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B97" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G97" s="5"/>
       <c r="H97" s="5">
@@ -4670,10 +4670,10 @@
         <v>2</v>
       </c>
       <c r="J97" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K97" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K97" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L97" s="5" t="s">
         <v>14</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G98" s="5"/>
       <c r="H98" s="5">
@@ -4717,22 +4717,22 @@
     </row>
     <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>23</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5">
@@ -4742,10 +4742,10 @@
         <v>0</v>
       </c>
       <c r="J99" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K99" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L99" s="5" t="s">
         <v>14</v>
@@ -4753,22 +4753,22 @@
     </row>
     <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B100" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5">
@@ -4778,10 +4778,10 @@
         <v>4</v>
       </c>
       <c r="J100" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K100" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K100" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L100" s="5" t="s">
         <v>14</v>
@@ -4789,22 +4789,22 @@
     </row>
     <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G101" s="5"/>
       <c r="H101" s="5">
@@ -4814,10 +4814,10 @@
         <v>150</v>
       </c>
       <c r="J101" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K101" s="13" t="s">
         <v>120</v>
-      </c>
-      <c r="K101" s="13" t="s">
-        <v>121</v>
       </c>
       <c r="L101" s="5" t="s">
         <v>14</v>
@@ -4825,22 +4825,22 @@
     </row>
     <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G102" s="5"/>
       <c r="H102" s="5">
@@ -4861,22 +4861,22 @@
     </row>
     <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>36</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G103" s="5"/>
       <c r="H103" s="5">
@@ -4886,10 +4886,10 @@
         <v>6</v>
       </c>
       <c r="J103" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K103" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L103" s="5" t="s">
         <v>14</v>
@@ -4897,22 +4897,22 @@
     </row>
     <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="5">
@@ -4922,10 +4922,10 @@
         <v>20</v>
       </c>
       <c r="J104" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K104" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K104" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L104" s="5" t="s">
         <v>14</v>
@@ -4933,22 +4933,22 @@
     </row>
     <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>39</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G105" s="5"/>
       <c r="H105" s="5">
@@ -4969,22 +4969,22 @@
     </row>
     <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B106" s="8" t="s">
         <v>39</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G106" s="5"/>
       <c r="H106" s="5">
@@ -4994,10 +4994,10 @@
         <v>8</v>
       </c>
       <c r="J106" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K106" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="K106" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="L106" s="5" t="s">
         <v>14</v>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CC5384-BEFC-49CC-A658-BD32D50925B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD49BB15-1D08-46B7-8A20-24CA6B8114D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$78</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="157">
   <si>
     <t>SKU</t>
   </si>
@@ -496,6 +496,18 @@
   </si>
   <si>
     <t>AMPM</t>
+  </si>
+  <si>
+    <t>FBK77102</t>
+  </si>
+  <si>
+    <t>FBM79585</t>
+  </si>
+  <si>
+    <t>TC40 RGB</t>
+  </si>
+  <si>
+    <t>Microphone Accessories</t>
   </si>
 </sst>
 </file>
@@ -668,7 +680,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="16">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -775,16 +787,6 @@
       </font>
       <fill>
         <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -1169,7 +1171,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L109"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -1334,16 +1336,16 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="2" t="s">
         <v>107</v>
       </c>
       <c r="E5" s="5" t="s">
@@ -1352,18 +1354,18 @@
       <c r="F5" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
+      <c r="G5" s="5"/>
       <c r="H5" s="5">
         <v>1244</v>
       </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5" t="s">
-        <v>150</v>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>14</v>
@@ -1371,16 +1373,16 @@
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>125</v>
@@ -1390,10 +1392,10 @@
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5">
-        <v>1244</v>
+        <v>1688</v>
       </c>
       <c r="I6" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="12" t="s">
         <v>152</v>
@@ -1407,35 +1409,35 @@
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>106</v>
+        <v>85</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="G7" s="5"/>
       <c r="H7" s="5">
-        <v>1688</v>
-      </c>
-      <c r="I7" s="5"/>
+        <v>1280</v>
+      </c>
+      <c r="I7" s="5">
+        <v>13</v>
+      </c>
       <c r="J7" s="5" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>14</v>
@@ -1443,29 +1445,29 @@
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>106</v>
+      <c r="D8" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5">
-        <v>1688</v>
+        <v>1280</v>
       </c>
       <c r="I8" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8" s="12" t="s">
         <v>152</v>
@@ -1478,16 +1480,16 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>33</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="8" t="s">
         <v>85</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -1500,14 +1502,14 @@
       <c r="H9" s="5">
         <v>1280</v>
       </c>
-      <c r="I9" s="5">
-        <v>13</v>
-      </c>
-      <c r="J9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>13</v>
+      <c r="I9" s="7">
+        <v>240</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>120</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>14</v>
@@ -1515,71 +1517,71 @@
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>85</v>
+        <v>147</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5">
-        <v>1280</v>
+        <v>652</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>33</v>
+      <c r="A11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>85</v>
+      <c r="D11" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5">
-        <v>1280</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="12" t="s">
-        <v>152</v>
+        <v>652</v>
+      </c>
+      <c r="I11" s="5">
+        <v>21</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>14</v>
@@ -1587,71 +1589,69 @@
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>33</v>
+        <v>61</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>85</v>
+      <c r="D12" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5">
-        <v>1280</v>
-      </c>
-      <c r="I12" s="7">
-        <v>240</v>
+        <v>12803</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>120</v>
+        <v>152</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>17</v>
+      <c r="A13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>64</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>134</v>
+      <c r="D13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F13" s="5">
+        <v>3</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="5">
-        <v>652</v>
-      </c>
-      <c r="I13" s="5">
+      <c r="H13" s="5"/>
+      <c r="I13" s="3">
         <v>0</v>
       </c>
-      <c r="J13" s="5" t="s">
-        <v>12</v>
+      <c r="J13" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>14</v>
@@ -1659,29 +1659,29 @@
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5">
-        <v>652</v>
+        <v>2412</v>
       </c>
       <c r="I14" s="5">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>12</v>
@@ -1694,72 +1694,72 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>17</v>
+      <c r="A15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>147</v>
+      <c r="D15" s="8" t="s">
+        <v>83</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5">
-        <v>652</v>
-      </c>
-      <c r="I15" s="5">
-        <v>3</v>
-      </c>
-      <c r="J15" s="5" t="s">
-        <v>150</v>
+        <v>2910</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>62</v>
+      <c r="A16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>95</v>
+      <c r="D16" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5">
-        <v>12803</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>152</v>
+        <v>1086</v>
+      </c>
+      <c r="I16" s="5">
+        <v>8</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>14</v>
@@ -1767,27 +1767,29 @@
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F17" s="5">
-        <v>3</v>
+        <v>94</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="H17" s="5">
+        <v>1086</v>
+      </c>
       <c r="I17" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J17" s="12" t="s">
         <v>152</v>
@@ -1800,36 +1802,36 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>19</v>
+      <c r="A18" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>149</v>
+      <c r="D18" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5">
-        <v>2412</v>
-      </c>
-      <c r="I18" s="5">
-        <v>1</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>13</v>
+        <v>1086</v>
+      </c>
+      <c r="I18" s="7">
+        <v>204</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>120</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>14</v>
@@ -1837,35 +1839,35 @@
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>149</v>
+        <v>101</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5">
-        <v>2412</v>
+        <v>603</v>
       </c>
       <c r="I19" s="5">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>14</v>
@@ -1873,29 +1875,29 @@
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>83</v>
+      <c r="D20" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5">
-        <v>2910</v>
+        <v>603</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20" s="12" t="s">
         <v>152</v>
@@ -1909,29 +1911,29 @@
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>123</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5">
-        <v>1086</v>
+        <v>1164</v>
       </c>
       <c r="I21" s="5">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>12</v>
@@ -1944,72 +1946,72 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>27</v>
+      <c r="A22" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>94</v>
+      <c r="D22" s="8" t="s">
+        <v>88</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>123</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5">
-        <v>1086</v>
-      </c>
-      <c r="I22" s="5">
-        <v>27</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>150</v>
+        <v>1164</v>
+      </c>
+      <c r="I22" s="3">
+        <v>11</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>27</v>
+      <c r="A23" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>38</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>94</v>
+      <c r="D23" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>123</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5">
-        <v>1086</v>
-      </c>
-      <c r="I23" s="3">
-        <v>5</v>
-      </c>
-      <c r="J23" s="12" t="s">
-        <v>152</v>
+        <v>845</v>
+      </c>
+      <c r="I23" s="5">
+        <v>20</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>14</v>
@@ -2017,35 +2019,35 @@
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>27</v>
+        <v>79</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>123</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5">
-        <v>1086</v>
-      </c>
-      <c r="I24" s="7">
-        <v>204</v>
+        <v>845</v>
+      </c>
+      <c r="I24" s="3">
+        <v>48</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>120</v>
+        <v>152</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="L24" s="5" t="s">
         <v>14</v>
@@ -2053,16 +2055,16 @@
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>123</v>
@@ -2072,10 +2074,10 @@
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5">
-        <v>603</v>
+        <v>1327</v>
       </c>
       <c r="I25" s="5">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>12</v>
@@ -2088,17 +2090,17 @@
       </c>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>31</v>
+      <c r="A26" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>101</v>
+      <c r="D26" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>123</v>
@@ -2108,16 +2110,16 @@
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5">
-        <v>603</v>
-      </c>
-      <c r="I26" s="5">
-        <v>2</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>150</v>
+        <v>1327</v>
+      </c>
+      <c r="I26" s="3">
+        <v>5</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L26" s="5" t="s">
         <v>14</v>
@@ -2125,16 +2127,16 @@
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="8" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>101</v>
+      <c r="D27" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>123</v>
@@ -2144,16 +2146,16 @@
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5">
-        <v>603</v>
-      </c>
-      <c r="I27" s="3">
-        <v>3</v>
+        <v>1327</v>
+      </c>
+      <c r="I27" s="11">
+        <v>30</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>45</v>
+        <v>121</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>120</v>
       </c>
       <c r="L27" s="5" t="s">
         <v>14</v>
@@ -2161,29 +2163,29 @@
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>123</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5">
-        <v>1164</v>
+        <v>2412</v>
       </c>
       <c r="I28" s="5">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>12</v>
@@ -2196,432 +2198,432 @@
       </c>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>22</v>
+      <c r="A29" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="6" t="s">
-        <v>88</v>
+      <c r="D29" s="2" t="s">
+        <v>98</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>123</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5">
-        <v>1164</v>
-      </c>
-      <c r="I29" s="5">
-        <v>5</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>150</v>
+        <v>2412</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>22</v>
+      <c r="A30" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="8" t="s">
-        <v>88</v>
+      <c r="D30" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5">
-        <v>1164</v>
-      </c>
-      <c r="I30" s="3">
-        <v>11</v>
-      </c>
-      <c r="J30" s="12" t="s">
-        <v>152</v>
+        <v>3015</v>
+      </c>
+      <c r="I30" s="5">
+        <v>4</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>38</v>
+      <c r="A31" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D31" s="6" t="s">
-        <v>111</v>
+      <c r="D31" s="8" t="s">
+        <v>86</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5">
-        <v>845</v>
-      </c>
-      <c r="I31" s="5">
-        <v>20</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>12</v>
+        <v>3015</v>
+      </c>
+      <c r="I31" s="3">
+        <v>6</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>38</v>
+      <c r="A32" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>111</v>
+      <c r="D32" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5">
-        <v>845</v>
-      </c>
-      <c r="I32" s="3">
-        <v>48</v>
-      </c>
-      <c r="J32" s="12" t="s">
-        <v>152</v>
+        <v>4423</v>
+      </c>
+      <c r="I32" s="5">
+        <v>9</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>21</v>
+      <c r="A33" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>24</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>87</v>
+      <c r="D33" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5">
-        <v>1327</v>
-      </c>
-      <c r="I33" s="5">
+        <v>4423</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L33" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5">
+        <v>4423</v>
+      </c>
+      <c r="I34" s="11">
+        <v>80</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="K34" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="J33" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K33" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L33" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="G34" s="5">
-        <v>0</v>
-      </c>
-      <c r="H34" s="5">
-        <v>1327</v>
-      </c>
-      <c r="I34" s="5"/>
-      <c r="J34" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="K34" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="L34" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>21</v>
-      </c>
       <c r="C35" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D35" s="8" t="s">
-        <v>87</v>
+      <c r="D35" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5">
         <v>1327</v>
       </c>
-      <c r="I35" s="3">
-        <v>5</v>
-      </c>
-      <c r="J35" s="12" t="s">
-        <v>152</v>
+      <c r="I35" s="5">
+        <v>2</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="L35" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>21</v>
+      <c r="A36" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>16</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>87</v>
+      <c r="D36" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5">
         <v>1327</v>
       </c>
-      <c r="I36" s="11">
-        <v>30</v>
-      </c>
-      <c r="J36" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="K36" s="13" t="s">
-        <v>120</v>
+      <c r="I36" s="5">
+        <v>36</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>28</v>
+      <c r="A37" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D37" s="6" t="s">
-        <v>98</v>
+      <c r="D37" s="2" t="s">
+        <v>90</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5">
-        <v>2412</v>
-      </c>
-      <c r="I37" s="5">
-        <v>9</v>
-      </c>
-      <c r="J37" s="5" t="s">
-        <v>12</v>
+        <v>1327</v>
+      </c>
+      <c r="I37" s="3">
+        <v>279</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="L37" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>28</v>
+      <c r="A38" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D38" s="6" t="s">
-        <v>98</v>
+      <c r="D38" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="G38" s="5">
+        <v>131</v>
+      </c>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5">
+        <v>1568</v>
+      </c>
+      <c r="I38" s="3">
         <v>0</v>
       </c>
-      <c r="H38" s="5">
-        <v>2412</v>
-      </c>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5" t="s">
-        <v>150</v>
+      <c r="J38" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>28</v>
+      <c r="A39" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>98</v>
+      <c r="D39" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5">
-        <v>2412</v>
-      </c>
-      <c r="I39" s="3">
-        <v>0</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>152</v>
+        <v>1448</v>
+      </c>
+      <c r="I39" s="5">
+        <v>9</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>20</v>
+      <c r="A40" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>34</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="6" t="s">
-        <v>86</v>
+      <c r="D40" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5">
-        <v>3015</v>
-      </c>
-      <c r="I40" s="5">
-        <v>4</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>12</v>
+        <v>1448</v>
+      </c>
+      <c r="I40" s="3">
+        <v>31</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="L40" s="5" t="s">
         <v>14</v>
@@ -2629,35 +2631,35 @@
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="5" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="G41" s="5">
-        <v>0</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="G41" s="5"/>
       <c r="H41" s="5">
-        <v>3015</v>
-      </c>
-      <c r="I41" s="5"/>
+        <v>1749</v>
+      </c>
+      <c r="I41" s="5">
+        <v>5</v>
+      </c>
       <c r="J41" s="5" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="L41" s="5" t="s">
         <v>14</v>
@@ -2665,29 +2667,29 @@
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D42" s="8" t="s">
-        <v>86</v>
+      <c r="D42" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5">
-        <v>3015</v>
+        <v>1749</v>
       </c>
       <c r="I42" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J42" s="12" t="s">
         <v>152</v>
@@ -2701,29 +2703,29 @@
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="5" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5">
-        <v>4423</v>
+        <v>1206</v>
       </c>
       <c r="I43" s="5">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J43" s="5" t="s">
         <v>12</v>
@@ -2736,72 +2738,72 @@
       </c>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>24</v>
+      <c r="A44" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D44" s="6" t="s">
-        <v>91</v>
+      <c r="D44" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="G44" s="5"/>
       <c r="H44" s="5">
-        <v>4423</v>
-      </c>
-      <c r="I44" s="5">
-        <v>2</v>
-      </c>
-      <c r="J44" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="K44" s="5" t="s">
-        <v>122</v>
+        <v>1206</v>
+      </c>
+      <c r="I44" s="9">
+        <v>20</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>45</v>
       </c>
       <c r="L44" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>24</v>
+      <c r="A45" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>91</v>
+      <c r="D45" s="5" t="s">
+        <v>115</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5">
-        <v>4423</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
+        <v>1206</v>
+      </c>
+      <c r="I45" s="5">
+        <v>3</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="K45" s="5" t="s">
-        <v>45</v>
+        <v>151</v>
+      </c>
+      <c r="K45" s="14" t="s">
+        <v>117</v>
       </c>
       <c r="L45" s="5" t="s">
         <v>14</v>
@@ -2809,35 +2811,35 @@
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E46" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5">
-        <v>4423</v>
-      </c>
-      <c r="I46" s="11">
-        <v>80</v>
+        <v>1206</v>
+      </c>
+      <c r="I46" s="3">
+        <v>5</v>
       </c>
       <c r="J46" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="K46" s="13" t="s">
-        <v>120</v>
+        <v>152</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="L46" s="5" t="s">
         <v>14</v>
@@ -2845,29 +2847,29 @@
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E47" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5">
-        <v>1327</v>
+        <v>1689</v>
       </c>
       <c r="I47" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J47" s="5" t="s">
         <v>12</v>
@@ -2880,36 +2882,36 @@
       </c>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>16</v>
+      <c r="A48" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>30</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D48" s="6" t="s">
-        <v>90</v>
+      <c r="D48" s="2" t="s">
+        <v>100</v>
       </c>
       <c r="E48" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5">
-        <v>1327</v>
-      </c>
-      <c r="I48" s="5">
-        <v>36</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>12</v>
+        <v>1689</v>
+      </c>
+      <c r="I48" s="3">
+        <v>188</v>
+      </c>
+      <c r="J48" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="L48" s="5" t="s">
         <v>14</v>
@@ -2917,35 +2919,35 @@
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E49" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5">
-        <v>1327</v>
+        <v>1930</v>
       </c>
       <c r="I49" s="5">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="J49" s="5" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="L49" s="5" t="s">
         <v>14</v>
@@ -2953,29 +2955,29 @@
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B50" s="8" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E50" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5">
-        <v>1327</v>
+        <v>1930</v>
       </c>
       <c r="I50" s="3">
-        <v>279</v>
+        <v>13</v>
       </c>
       <c r="J50" s="12" t="s">
         <v>152</v>
@@ -2989,35 +2991,35 @@
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="E51" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5">
-        <v>1568</v>
+        <v>1930</v>
       </c>
       <c r="I51" s="5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="L51" s="5" t="s">
         <v>14</v>
@@ -3025,29 +3027,29 @@
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="E52" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5">
-        <v>1568</v>
+        <v>1930</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="J52" s="12" t="s">
         <v>152</v>
@@ -3061,29 +3063,29 @@
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="5" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="E53" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5">
-        <v>1448</v>
+        <v>1206</v>
       </c>
       <c r="I53" s="5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J53" s="5" t="s">
         <v>12</v>
@@ -3097,35 +3099,35 @@
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="5" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="E54" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5">
-        <v>1448</v>
+        <v>1206</v>
       </c>
       <c r="I54" s="5">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J54" s="5" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>14</v>
@@ -3133,29 +3135,29 @@
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D55" s="2" t="s">
-        <v>110</v>
+      <c r="D55" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="E55" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5">
-        <v>1448</v>
+        <v>1206</v>
       </c>
       <c r="I55" s="3">
-        <v>31</v>
+        <v>359</v>
       </c>
       <c r="J55" s="12" t="s">
         <v>152</v>
@@ -3169,107 +3171,107 @@
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="5" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D56" s="6" t="s">
-        <v>104</v>
+      <c r="D56" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="E56" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5">
-        <v>1749</v>
+        <v>1206</v>
       </c>
       <c r="I56" s="5">
-        <v>5</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K56" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
+      </c>
+      <c r="J56" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="K56" s="14" t="s">
+        <v>117</v>
       </c>
       <c r="L56" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>35</v>
+      <c r="A57" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>32</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D57" s="6" t="s">
-        <v>104</v>
+      <c r="D57" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5">
-        <v>1749</v>
-      </c>
-      <c r="I57" s="5">
-        <v>4</v>
-      </c>
-      <c r="J57" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="K57" s="5" t="s">
-        <v>122</v>
+        <v>1086</v>
+      </c>
+      <c r="I57" s="9">
+        <v>30</v>
+      </c>
+      <c r="J57" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>45</v>
       </c>
       <c r="L57" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="B58" s="8" t="s">
-        <v>35</v>
+      <c r="A58" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>104</v>
+      <c r="D58" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>126</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5">
-        <v>1749</v>
-      </c>
-      <c r="I58" s="3">
-        <v>10</v>
-      </c>
-      <c r="J58" s="12" t="s">
-        <v>152</v>
+        <v>1086</v>
+      </c>
+      <c r="I58" s="5">
+        <v>11</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="L58" s="5" t="s">
         <v>14</v>
@@ -3277,16 +3279,16 @@
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D59" s="6" t="s">
-        <v>115</v>
+      <c r="D59" s="5" t="s">
+        <v>118</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>126</v>
@@ -3296,33 +3298,33 @@
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5">
-        <v>1206</v>
+        <v>1086</v>
       </c>
       <c r="I59" s="5">
-        <v>27</v>
-      </c>
-      <c r="J59" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K59" s="5" t="s">
-        <v>13</v>
+        <v>4</v>
+      </c>
+      <c r="J59" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="K59" s="14" t="s">
+        <v>117</v>
       </c>
       <c r="L59" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>29</v>
+      <c r="A60" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>32</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D60" s="6" t="s">
-        <v>115</v>
+      <c r="D60" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>126</v>
@@ -3332,88 +3334,88 @@
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5">
-        <v>1206</v>
-      </c>
-      <c r="I60" s="5">
-        <v>6</v>
-      </c>
-      <c r="J60" s="5" t="s">
-        <v>150</v>
+        <v>1086</v>
+      </c>
+      <c r="I60" s="3">
+        <v>379</v>
+      </c>
+      <c r="J60" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L60" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>29</v>
+      <c r="A61" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>41</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>115</v>
+      <c r="D61" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5">
-        <v>1206</v>
-      </c>
-      <c r="I61" s="9">
-        <v>20</v>
-      </c>
-      <c r="J61" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="K61" s="14" t="s">
-        <v>45</v>
+        <v>823</v>
+      </c>
+      <c r="I61" s="5">
+        <v>3</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="L61" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>29</v>
+      <c r="A62" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D62" s="5" t="s">
-        <v>115</v>
+      <c r="D62" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5">
-        <v>1206</v>
-      </c>
-      <c r="I62" s="5">
-        <v>3</v>
+        <v>823</v>
+      </c>
+      <c r="I62" s="3">
+        <v>1</v>
       </c>
       <c r="J62" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="K62" s="14" t="s">
-        <v>117</v>
+        <v>152</v>
+      </c>
+      <c r="K62" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="L62" s="5" t="s">
         <v>14</v>
@@ -3421,35 +3423,35 @@
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>29</v>
+        <v>80</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5">
-        <v>1206</v>
-      </c>
-      <c r="I63" s="3">
-        <v>5</v>
+        <v>823</v>
+      </c>
+      <c r="I63" s="7">
+        <v>504</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="K63" s="5" t="s">
-        <v>45</v>
+        <v>119</v>
+      </c>
+      <c r="K63" s="13" t="s">
+        <v>120</v>
       </c>
       <c r="L63" s="5" t="s">
         <v>14</v>
@@ -3457,29 +3459,29 @@
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5">
-        <v>1689</v>
+        <v>921</v>
       </c>
       <c r="I64" s="5">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>12</v>
@@ -3492,36 +3494,36 @@
       </c>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>30</v>
+      <c r="A65" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>100</v>
+      <c r="D65" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5">
-        <v>1689</v>
-      </c>
-      <c r="I65" s="5">
-        <v>7</v>
-      </c>
-      <c r="J65" s="5" t="s">
-        <v>150</v>
+        <v>921</v>
+      </c>
+      <c r="I65" s="3">
+        <v>100</v>
+      </c>
+      <c r="J65" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L65" s="5" t="s">
         <v>14</v>
@@ -3529,35 +3531,35 @@
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5">
-        <v>1689</v>
-      </c>
-      <c r="I66" s="3">
-        <v>188</v>
+        <v>921</v>
+      </c>
+      <c r="I66" s="10">
+        <v>256</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="K66" s="5" t="s">
-        <v>45</v>
+        <v>121</v>
+      </c>
+      <c r="K66" s="13" t="s">
+        <v>120</v>
       </c>
       <c r="L66" s="5" t="s">
         <v>14</v>
@@ -3565,29 +3567,29 @@
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F67" s="5" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5">
-        <v>1930</v>
+        <v>2412</v>
       </c>
       <c r="I67" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>12</v>
@@ -3601,35 +3603,35 @@
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5">
-        <v>1930</v>
+        <v>2412</v>
       </c>
       <c r="I68" s="5">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="L68" s="5" t="s">
         <v>14</v>
@@ -3637,29 +3639,29 @@
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F69" s="5" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="G69" s="5"/>
       <c r="H69" s="5">
-        <v>1930</v>
+        <v>2412</v>
       </c>
       <c r="I69" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J69" s="12" t="s">
         <v>152</v>
@@ -3673,29 +3675,29 @@
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="5" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G70" s="5"/>
       <c r="H70" s="5">
-        <v>1930</v>
+        <v>3491</v>
       </c>
       <c r="I70" s="5">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>12</v>
@@ -3708,144 +3710,144 @@
       </c>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>26</v>
+      <c r="A71" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>37</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D71" s="6" t="s">
-        <v>93</v>
+      <c r="D71" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5">
-        <v>1930</v>
-      </c>
-      <c r="I71" s="5">
-        <v>9</v>
-      </c>
-      <c r="J71" s="5" t="s">
-        <v>150</v>
+        <v>3491</v>
+      </c>
+      <c r="I71" s="3">
+        <v>2</v>
+      </c>
+      <c r="J71" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="L71" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>26</v>
+      <c r="A72" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>93</v>
+      <c r="D72" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5">
-        <v>1930</v>
-      </c>
-      <c r="I72" s="3">
-        <v>52</v>
-      </c>
-      <c r="J72" s="12" t="s">
-        <v>152</v>
+        <v>1448</v>
+      </c>
+      <c r="I72" s="5">
+        <v>17</v>
+      </c>
+      <c r="J72" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="L72" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>15</v>
+      <c r="A73" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>23</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D73" s="6" t="s">
-        <v>84</v>
+      <c r="D73" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5">
-        <v>1206</v>
-      </c>
-      <c r="I73" s="5">
-        <v>0</v>
-      </c>
-      <c r="J73" s="5" t="s">
-        <v>12</v>
+        <v>1448</v>
+      </c>
+      <c r="I73" s="3">
+        <v>4</v>
+      </c>
+      <c r="J73" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="L73" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>15</v>
+      <c r="A74" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D74" s="6" t="s">
-        <v>84</v>
+      <c r="D74" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5">
-        <v>1206</v>
-      </c>
-      <c r="I74" s="5">
-        <v>10</v>
-      </c>
-      <c r="J74" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K74" s="5" t="s">
-        <v>13</v>
+        <v>1448</v>
+      </c>
+      <c r="I74" s="7">
+        <v>150</v>
+      </c>
+      <c r="J74" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K74" s="13" t="s">
+        <v>120</v>
       </c>
       <c r="L74" s="5" t="s">
         <v>14</v>
@@ -3853,35 +3855,35 @@
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="5" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>82</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5">
-        <v>1206</v>
+        <v>965</v>
       </c>
       <c r="I75" s="5">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="J75" s="5" t="s">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>122</v>
+        <v>13</v>
       </c>
       <c r="L75" s="5" t="s">
         <v>14</v>
@@ -3889,29 +3891,29 @@
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D76" s="8" t="s">
-        <v>84</v>
+      <c r="D76" s="2" t="s">
+        <v>105</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="5">
-        <v>1206</v>
+        <v>965</v>
       </c>
       <c r="I76" s="3">
-        <v>359</v>
+        <v>20</v>
       </c>
       <c r="J76" s="12" t="s">
         <v>152</v>
@@ -3925,1109 +3927,997 @@
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D77" s="5" t="s">
-        <v>84</v>
+      <c r="D77" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5">
-        <v>1206</v>
+        <v>1397</v>
       </c>
       <c r="I77" s="5">
-        <v>2</v>
-      </c>
-      <c r="J77" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="K77" s="14" t="s">
-        <v>117</v>
+        <v>8</v>
+      </c>
+      <c r="J77" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K77" s="5" t="s">
+        <v>13</v>
       </c>
       <c r="L77" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>32</v>
+      <c r="A78" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>116</v>
+      <c r="D78" s="2" t="s">
+        <v>108</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5">
-        <v>1086</v>
-      </c>
-      <c r="I78" s="9">
+        <v>1397</v>
+      </c>
+      <c r="I78" s="3">
+        <v>8</v>
+      </c>
+      <c r="J78" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K78" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="L78" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I79" s="1">
+        <v>43</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L79" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I80" s="1">
+        <v>0</v>
+      </c>
+      <c r="J80" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L80" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I81" s="1">
+        <v>31</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L81" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I82" s="1">
+        <v>5</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L82" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J78" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="K78" s="14" t="s">
-        <v>45</v>
-      </c>
-      <c r="L78" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="5" t="s">
+      <c r="C83" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I83" s="1">
+        <v>5</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L83" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B84" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C79" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D79" s="6" t="s">
+      <c r="C84" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="E79" s="5" t="s">
+      <c r="E84" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F79" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="G79" s="5"/>
-      <c r="H79" s="5">
-        <v>1086</v>
-      </c>
-      <c r="I79" s="5">
-        <v>11</v>
-      </c>
-      <c r="J79" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K79" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L79" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E80" s="5" t="s">
+      <c r="I84" s="1">
+        <v>23</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L84" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I85" s="1">
+        <v>3</v>
+      </c>
+      <c r="J85" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L85" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I86" s="1">
+        <v>8</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L86" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I87" s="1">
+        <v>0</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L87" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I88" s="1">
+        <v>0</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L88" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I89" s="1">
+        <v>29</v>
+      </c>
+      <c r="J89" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K89" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L89" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I90" s="1">
+        <v>2</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L90" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I91" s="1">
+        <v>4</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L91" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I92" s="1">
+        <v>1</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L92" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I93" s="1">
+        <v>0</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L93" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E94" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F80" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="G80" s="5"/>
-      <c r="H80" s="5">
-        <v>1086</v>
-      </c>
-      <c r="I80" s="5">
-        <v>14</v>
-      </c>
-      <c r="J80" s="5" t="s">
+      <c r="I94" s="1">
+        <v>2</v>
+      </c>
+      <c r="J94" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K80" s="5" t="s">
+      <c r="K94" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="L80" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E81" s="5" t="s">
+      <c r="L94" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E95" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F81" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="G81" s="5"/>
-      <c r="H81" s="5">
-        <v>1086</v>
-      </c>
-      <c r="I81" s="5">
+      <c r="I95" s="1">
+        <v>1</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L95" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I96" s="1">
+        <v>2</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L96" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I97" s="1">
+        <v>9</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L97" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I98" s="1">
         <v>4</v>
       </c>
-      <c r="J81" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="K81" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="L81" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="B82" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E82" s="5" t="s">
+      <c r="J98" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L98" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I99" s="1">
+        <v>5</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L99" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I100" s="1">
+        <v>0</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L100" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I101" s="1">
+        <v>0</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L101" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I102" s="1">
+        <v>0</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L102" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I103" s="1">
+        <v>0</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L103" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I104" s="1">
+        <v>0</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K104" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L104" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I105" s="1">
+        <v>0</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L105" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I106" s="1">
+        <v>35</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L106" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F82" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="G82" s="5"/>
-      <c r="H82" s="5">
-        <v>1086</v>
-      </c>
-      <c r="I82" s="3">
-        <v>379</v>
-      </c>
-      <c r="J82" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="K82" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L82" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F83" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="G83" s="5"/>
-      <c r="H83" s="5">
-        <v>823</v>
-      </c>
-      <c r="I83" s="5">
-        <v>3</v>
-      </c>
-      <c r="J83" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K83" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L83" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="G84" s="5"/>
-      <c r="H84" s="5">
-        <v>823</v>
-      </c>
-      <c r="I84" s="5">
+      <c r="I107" s="1">
+        <v>2</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L107" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I108" s="1">
+        <v>9</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L108" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I109" s="1">
         <v>0</v>
       </c>
-      <c r="J84" s="5" t="s">
+      <c r="J109" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="K84" s="5" t="s">
+      <c r="K109" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="L84" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B85" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="G85" s="5"/>
-      <c r="H85" s="5">
-        <v>823</v>
-      </c>
-      <c r="I85" s="3">
-        <v>1</v>
-      </c>
-      <c r="J85" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="K85" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L85" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="B86" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="G86" s="5"/>
-      <c r="H86" s="5">
-        <v>823</v>
-      </c>
-      <c r="I86" s="7">
-        <v>504</v>
-      </c>
-      <c r="J86" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="K86" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="L86" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G87" s="5"/>
-      <c r="H87" s="5">
-        <v>921</v>
-      </c>
-      <c r="I87" s="5">
-        <v>40</v>
-      </c>
-      <c r="J87" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K87" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L87" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G88" s="5"/>
-      <c r="H88" s="5">
-        <v>921</v>
-      </c>
-      <c r="I88" s="5">
-        <v>44</v>
-      </c>
-      <c r="J88" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="K88" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="L88" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G89" s="5"/>
-      <c r="H89" s="5">
-        <v>921</v>
-      </c>
-      <c r="I89" s="3">
-        <v>100</v>
-      </c>
-      <c r="J89" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="K89" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L89" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="B90" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G90" s="5"/>
-      <c r="H90" s="5">
-        <v>921</v>
-      </c>
-      <c r="I90" s="10">
-        <v>256</v>
-      </c>
-      <c r="J90" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="K90" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="L90" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G91" s="5"/>
-      <c r="H91" s="5">
-        <v>2412</v>
-      </c>
-      <c r="I91" s="5">
-        <v>0</v>
-      </c>
-      <c r="J91" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K91" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L91" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G92" s="5"/>
-      <c r="H92" s="5">
-        <v>2412</v>
-      </c>
-      <c r="I92" s="5">
-        <v>13</v>
-      </c>
-      <c r="J92" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K92" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L92" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G93" s="5"/>
-      <c r="H93" s="5">
-        <v>2412</v>
-      </c>
-      <c r="I93" s="5">
-        <v>7</v>
-      </c>
-      <c r="J93" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="K93" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="L93" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G94" s="5"/>
-      <c r="H94" s="5">
-        <v>2412</v>
-      </c>
-      <c r="I94" s="3">
-        <v>11</v>
-      </c>
-      <c r="J94" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="K94" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L94" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G95" s="5"/>
-      <c r="H95" s="5">
-        <v>3491</v>
-      </c>
-      <c r="I95" s="5">
-        <v>3</v>
-      </c>
-      <c r="J95" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K95" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L95" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G96" s="5">
-        <v>0</v>
-      </c>
-      <c r="H96" s="5">
-        <v>3491</v>
-      </c>
-      <c r="I96" s="5"/>
-      <c r="J96" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="K96" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="L96" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B97" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G97" s="5"/>
-      <c r="H97" s="5">
-        <v>3491</v>
-      </c>
-      <c r="I97" s="3">
-        <v>2</v>
-      </c>
-      <c r="J97" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="K97" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L97" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="G98" s="5"/>
-      <c r="H98" s="5">
-        <v>1448</v>
-      </c>
-      <c r="I98" s="5">
-        <v>17</v>
-      </c>
-      <c r="J98" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K98" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L98" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="G99" s="5"/>
-      <c r="H99" s="5">
-        <v>1448</v>
-      </c>
-      <c r="I99" s="5">
-        <v>0</v>
-      </c>
-      <c r="J99" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="K99" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="L99" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B100" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F100" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="G100" s="5"/>
-      <c r="H100" s="5">
-        <v>1448</v>
-      </c>
-      <c r="I100" s="3">
-        <v>4</v>
-      </c>
-      <c r="J100" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="K100" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L100" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F101" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="G101" s="5"/>
-      <c r="H101" s="5">
-        <v>1448</v>
-      </c>
-      <c r="I101" s="7">
-        <v>150</v>
-      </c>
-      <c r="J101" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="K101" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="L101" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D102" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E102" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F102" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="G102" s="5"/>
-      <c r="H102" s="5">
-        <v>965</v>
-      </c>
-      <c r="I102" s="5">
-        <v>63</v>
-      </c>
-      <c r="J102" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K102" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L102" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F103" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="G103" s="5"/>
-      <c r="H103" s="5">
-        <v>965</v>
-      </c>
-      <c r="I103" s="5">
-        <v>6</v>
-      </c>
-      <c r="J103" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="K103" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="L103" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B104" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F104" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="G104" s="5"/>
-      <c r="H104" s="5">
-        <v>965</v>
-      </c>
-      <c r="I104" s="3">
-        <v>20</v>
-      </c>
-      <c r="J104" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="K104" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L104" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F105" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G105" s="5"/>
-      <c r="H105" s="5">
-        <v>1397</v>
-      </c>
-      <c r="I105" s="5">
-        <v>8</v>
-      </c>
-      <c r="J105" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="K105" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="L105" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="B106" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5">
-        <v>1397</v>
-      </c>
-      <c r="I106" s="3">
-        <v>8</v>
-      </c>
-      <c r="J106" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="K106" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="L106" s="5" t="s">
+      <c r="L109" s="5" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L106" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
+  <autoFilter ref="A1:L78" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A5:A8">
-    <cfRule type="duplicateValues" dxfId="16" priority="844"/>
+  <conditionalFormatting sqref="A5:A6">
+    <cfRule type="duplicateValues" dxfId="15" priority="856"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A10:A12">
-    <cfRule type="duplicateValues" dxfId="15" priority="828"/>
+  <conditionalFormatting sqref="A8:A9">
+    <cfRule type="duplicateValues" dxfId="14" priority="847"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A19">
-    <cfRule type="duplicateValues" dxfId="14" priority="105"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A20 A22:A24">
-    <cfRule type="duplicateValues" dxfId="13" priority="826"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="827"/>
+  <conditionalFormatting sqref="A15 A17:A18">
+    <cfRule type="duplicateValues" dxfId="13" priority="845"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
     <cfRule type="duplicateValues" dxfId="11" priority="821"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D12">
-    <cfRule type="duplicateValues" dxfId="10" priority="217"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="218"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="219" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="220" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="221" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D7:D9">
+    <cfRule type="duplicateValues" dxfId="10" priority="848"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="849"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="850" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="851" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="852" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
     <cfRule type="duplicateValues" dxfId="5" priority="824"/>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 15\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8EB3853-0467-42AE-9330-71CC743044B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1CD440-6573-41BA-8612-57C3F6482F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$97</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="147">
   <si>
     <t>SKU</t>
   </si>
@@ -87,9 +87,6 @@
     <t>FBA79111</t>
   </si>
   <si>
-    <t>FBA79263</t>
-  </si>
-  <si>
     <t>FBA77103</t>
   </si>
   <si>
@@ -171,9 +168,6 @@
     <t>B0BRKFP94K</t>
   </si>
   <si>
-    <t>B0CYSLCRQS</t>
-  </si>
-  <si>
     <t>B09Z5Q194D</t>
   </si>
   <si>
@@ -243,9 +237,6 @@
     <t>B0CQX4K9P5</t>
   </si>
   <si>
-    <t>TONOR</t>
-  </si>
-  <si>
     <t>Amazon</t>
   </si>
   <si>
@@ -372,9 +363,6 @@
     <t>Tonor</t>
   </si>
   <si>
-    <t>MR-01</t>
-  </si>
-  <si>
     <t>Q9</t>
   </si>
   <si>
@@ -423,18 +411,9 @@
     <t>Hand held Mic</t>
   </si>
   <si>
-    <t>Home &amp; Kitchen</t>
-  </si>
-  <si>
-    <t>Cleaning &amp; Vacumming</t>
-  </si>
-  <si>
     <t>USB/XLR Mic</t>
   </si>
   <si>
-    <t>Mite Remover</t>
-  </si>
-  <si>
     <t>Stand</t>
   </si>
   <si>
@@ -496,16 +475,17 @@
   </si>
   <si>
     <t>1p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+K1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -562,12 +542,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1F2937"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -613,12 +587,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -647,215 +620,18 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="48">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="43">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1086,6 +862,140 @@
       <font>
         <condense val="0"/>
         <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1555,19 +1465,19 @@
         <v>14</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="7">
@@ -1577,281 +1487,281 @@
         <v>10</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>99</v>
+        <v>107</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7">
-        <v>652</v>
-      </c>
-      <c r="I3" s="10">
-        <v>1026</v>
+        <v>2412</v>
+      </c>
+      <c r="I3" s="8">
+        <v>12</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="K3" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="L3" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>125</v>
-      </c>
       <c r="F4" s="7" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="7">
-        <v>2412</v>
-      </c>
-      <c r="I4" s="8">
-        <v>12</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>116</v>
+        <v>1244</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>102</v>
+      <c r="C5" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="7">
         <v>1244</v>
       </c>
-      <c r="I5" s="8"/>
-      <c r="J5" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>105</v>
+      <c r="I5" s="8">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>76</v>
+      <c r="A6" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>102</v>
+        <v>107</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="7">
-        <v>1244</v>
-      </c>
-      <c r="I6" s="8">
-        <v>0</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>116</v>
+        <v>1688</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>82</v>
+      <c r="C7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7">
         <v>1688</v>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>105</v>
+      <c r="I7" s="8">
+        <v>2</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>75</v>
+      <c r="A8" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>82</v>
+        <v>107</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="7">
-        <v>1688</v>
+        <v>1280</v>
       </c>
       <c r="I8" s="8">
-        <v>2</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>116</v>
+        <v>11</v>
+      </c>
+      <c r="J8" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>104</v>
+        <v>57</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>101</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="7">
         <v>1280</v>
       </c>
       <c r="I9" s="8">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>104</v>
+      <c r="A10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="7">
@@ -1860,86 +1770,86 @@
       <c r="I10" s="8">
         <v>0</v>
       </c>
-      <c r="J10" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>105</v>
+      <c r="J10" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>59</v>
+      <c r="A11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="7">
-        <v>1280</v>
+        <v>652</v>
       </c>
       <c r="I11" s="8">
         <v>0</v>
       </c>
-      <c r="J11" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>116</v>
+      <c r="J11" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>59</v>
+      <c r="A12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>41</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="7">
-        <v>1280</v>
-      </c>
-      <c r="I12" s="10">
-        <v>240</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>120</v>
+        <v>652</v>
+      </c>
+      <c r="I12" s="8">
+        <v>10</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K12" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1947,1651 +1857,1649 @@
         <v>14</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>99</v>
+        <v>41</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>96</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="7">
         <v>652</v>
       </c>
       <c r="I13" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>99</v>
+      <c r="A14" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="7">
-        <v>652</v>
+        <v>12803</v>
       </c>
       <c r="I14" s="8">
-        <v>10</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>99</v>
+        <v>43</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="7">
-        <v>652</v>
+        <v>2412</v>
       </c>
       <c r="I15" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>109</v>
+      <c r="A16" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>113</v>
+        <v>107</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>97</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="7">
-        <v>12803</v>
+        <v>2412</v>
       </c>
       <c r="I16" s="8">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>116</v>
+        <v>2</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>16</v>
+        <v>103</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="14" t="s">
-        <v>111</v>
+        <v>107</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>108</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="G17" s="7" t="s">
-        <v>131</v>
-      </c>
+      <c r="G17" s="7"/>
       <c r="H17" s="7">
-        <v>1162</v>
-      </c>
-      <c r="I17" s="10">
-        <v>1002</v>
+        <v>2910</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="K17" s="11" t="s">
-        <v>120</v>
+        <v>142</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>68</v>
+        <v>51</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="7">
-        <v>2412</v>
+        <v>1086</v>
       </c>
       <c r="I18" s="8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>110</v>
+        <v>51</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="7">
-        <v>2412</v>
+        <v>1086</v>
       </c>
       <c r="I19" s="8">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>112</v>
+        <v>107</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="7">
-        <v>2910</v>
+        <v>1086</v>
       </c>
       <c r="I20" s="8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>68</v>
+        <v>55</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="7">
-        <v>1086</v>
+        <v>603</v>
       </c>
       <c r="I21" s="8">
         <v>8</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>110</v>
+        <v>55</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="7">
-        <v>1086</v>
+        <v>603</v>
       </c>
       <c r="I22" s="8">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="7">
-        <v>1086</v>
+        <v>603</v>
       </c>
       <c r="I23" s="8">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>53</v>
+      <c r="A24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>46</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>86</v>
+        <v>107</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="7">
-        <v>1086</v>
-      </c>
-      <c r="I24" s="10">
-        <v>204</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="K24" s="11" t="s">
-        <v>120</v>
+        <v>1164</v>
+      </c>
+      <c r="I24" s="8">
+        <v>38</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="8" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>85</v>
+        <v>46</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>76</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="7">
-        <v>603</v>
+        <v>1164</v>
       </c>
       <c r="I25" s="8">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>85</v>
+      <c r="A26" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>76</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="7">
-        <v>603</v>
+        <v>1164</v>
       </c>
       <c r="I26" s="8">
-        <v>2</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>105</v>
+        <v>11</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>57</v>
+      <c r="A27" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>62</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>85</v>
+        <v>107</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="7">
-        <v>603</v>
+        <v>845</v>
       </c>
       <c r="I27" s="8">
-        <v>3</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>116</v>
+        <v>20</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>79</v>
+      <c r="A28" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="7">
-        <v>1164</v>
+        <v>845</v>
       </c>
       <c r="I28" s="8">
-        <v>38</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>70</v>
+        <v>48</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>79</v>
+        <v>45</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="7">
-        <v>1164</v>
+        <v>1327</v>
       </c>
       <c r="I29" s="8">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>48</v>
+      <c r="A30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>79</v>
+        <v>107</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="7">
-        <v>1164</v>
-      </c>
-      <c r="I30" s="8">
-        <v>11</v>
-      </c>
-      <c r="J30" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>116</v>
+        <v>1327</v>
+      </c>
+      <c r="I30" s="8"/>
+      <c r="J30" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>115</v>
+      <c r="A31" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>144</v>
+        <v>127</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="7">
-        <v>845</v>
+        <v>1327</v>
       </c>
       <c r="I31" s="8">
-        <v>20</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>70</v>
+        <v>5</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>64</v>
+      <c r="A32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>115</v>
+        <v>107</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="7">
-        <v>845</v>
+        <v>2412</v>
       </c>
       <c r="I32" s="8">
-        <v>48</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>116</v>
+        <v>9</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K32" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L32" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>88</v>
+        <v>52</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>94</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="7">
-        <v>1327</v>
-      </c>
-      <c r="I33" s="8">
-        <v>15</v>
-      </c>
+        <v>2412</v>
+      </c>
+      <c r="I33" s="8"/>
       <c r="J33" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L33" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D34" s="8" t="s">
-        <v>88</v>
+      <c r="A34" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="7">
-        <v>1327</v>
-      </c>
-      <c r="I34" s="8"/>
-      <c r="J34" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K34" s="7" t="s">
-        <v>105</v>
+        <v>2412</v>
+      </c>
+      <c r="I34" s="8">
+        <v>0</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>47</v>
+      <c r="A35" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D35" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>88</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="7">
-        <v>1327</v>
+        <v>3015</v>
       </c>
       <c r="I35" s="8">
-        <v>5</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>116</v>
+        <v>4</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K35" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>47</v>
+      <c r="A36" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>44</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D36" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>88</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="7">
-        <v>1327</v>
-      </c>
-      <c r="I36" s="15">
-        <v>30</v>
-      </c>
-      <c r="J36" s="9" t="s">
+        <v>3015</v>
+      </c>
+      <c r="I36" s="8"/>
+      <c r="J36" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K36" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="L36" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="K36" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="L36" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>123</v>
-      </c>
       <c r="F37" s="7" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="7">
-        <v>2412</v>
+        <v>3015</v>
       </c>
       <c r="I37" s="8">
-        <v>9</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>70</v>
+        <v>6</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L37" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>97</v>
+        <v>48</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="7">
-        <v>2412</v>
-      </c>
-      <c r="I38" s="8"/>
+        <v>4423</v>
+      </c>
+      <c r="I38" s="8">
+        <v>9</v>
+      </c>
       <c r="J38" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K38" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L38" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>54</v>
+      <c r="A39" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>97</v>
+        <v>107</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>100</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="7">
-        <v>2412</v>
+        <v>4423</v>
       </c>
       <c r="I39" s="8">
-        <v>0</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>116</v>
+        <v>1</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K39" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L39" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>91</v>
+      <c r="A40" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="7">
-        <v>3015</v>
+        <v>4423</v>
       </c>
       <c r="I40" s="8">
-        <v>4</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K40" s="7" t="s">
-        <v>70</v>
+        <v>0</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L40" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="8" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>91</v>
+        <v>40</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="7">
-        <v>3015</v>
-      </c>
-      <c r="I41" s="8"/>
+        <v>1327</v>
+      </c>
+      <c r="I41" s="8">
+        <v>0</v>
+      </c>
       <c r="J41" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L41" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>46</v>
+      <c r="A42" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>40</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>91</v>
+        <v>107</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>90</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="7">
-        <v>3015</v>
+        <v>1327</v>
       </c>
       <c r="I42" s="8">
-        <v>6</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>116</v>
+        <v>35</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K42" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L42" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>103</v>
+        <v>40</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>90</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="7">
-        <v>4423</v>
+        <v>1327</v>
       </c>
       <c r="I43" s="8">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K43" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L43" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D44" s="8" t="s">
-        <v>103</v>
+      <c r="A44" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="7">
-        <v>4423</v>
+        <v>1327</v>
       </c>
       <c r="I44" s="8">
-        <v>1</v>
-      </c>
-      <c r="J44" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K44" s="7" t="s">
-        <v>105</v>
+        <v>279</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L44" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>50</v>
+      <c r="A45" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>71</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="7">
-        <v>4423</v>
+        <v>1568</v>
       </c>
       <c r="I45" s="8">
-        <v>0</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>116</v>
+        <v>9</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L45" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>103</v>
+        <v>107</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="7">
-        <v>4423</v>
-      </c>
-      <c r="I46" s="15">
-        <v>80</v>
+        <v>1568</v>
+      </c>
+      <c r="I46" s="8">
+        <v>0</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="K46" s="11" t="s">
-        <v>120</v>
+        <v>142</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L46" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>68</v>
+        <v>58</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="7">
-        <v>1327</v>
+        <v>1448</v>
       </c>
       <c r="I47" s="8">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K47" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L47" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="8" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>93</v>
+        <v>58</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="7">
-        <v>1327</v>
+        <v>1448</v>
       </c>
       <c r="I48" s="8">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L48" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>93</v>
+      <c r="A49" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="7">
-        <v>1327</v>
+        <v>1448</v>
       </c>
       <c r="I49" s="8">
-        <v>27</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K49" s="7" t="s">
-        <v>105</v>
+        <v>36</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L49" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>41</v>
+      <c r="A50" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D50" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" s="7" t="s">
         <v>93</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="7">
-        <v>1327</v>
+        <v>1749</v>
       </c>
       <c r="I50" s="8">
-        <v>279</v>
-      </c>
-      <c r="J50" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>116</v>
+        <v>5</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K50" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L50" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="B51" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>110</v>
+        <v>59</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="7">
-        <v>1568</v>
+        <v>1749</v>
       </c>
       <c r="I51" s="8">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="7">
-        <v>1568</v>
+        <v>1749</v>
       </c>
       <c r="I52" s="8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L52" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C53" s="8" t="s">
-        <v>68</v>
+        <v>53</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="7">
-        <v>1448</v>
+        <v>1206</v>
       </c>
       <c r="I53" s="8">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="J53" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K53" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L53" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C54" s="8" t="s">
-        <v>110</v>
+        <v>53</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="7">
-        <v>1448</v>
+        <v>1206</v>
       </c>
       <c r="I54" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J54" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K54" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L54" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>60</v>
+      <c r="A55" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>78</v>
+        <v>107</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="7">
-        <v>1448</v>
-      </c>
-      <c r="I55" s="8">
-        <v>36</v>
+        <v>1206</v>
+      </c>
+      <c r="I55" s="10">
+        <v>20</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>116</v>
+        <v>143</v>
+      </c>
+      <c r="K55" s="11" t="s">
+        <v>112</v>
       </c>
       <c r="L55" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B56" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>96</v>
+        <v>26</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>89</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="7">
-        <v>1749</v>
+        <v>1206</v>
       </c>
       <c r="I56" s="8">
-        <v>5</v>
-      </c>
-      <c r="J56" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K56" s="7" t="s">
-        <v>70</v>
+        <v>3</v>
+      </c>
+      <c r="J56" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="K56" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="L56" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B57" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>96</v>
+      <c r="A57" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="7">
-        <v>1749</v>
+        <v>1206</v>
       </c>
       <c r="I57" s="8">
-        <v>4</v>
-      </c>
-      <c r="J57" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K57" s="7" t="s">
-        <v>105</v>
+        <v>5</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L57" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>61</v>
+      <c r="A58" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>96</v>
+        <v>107</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="7">
-        <v>1749</v>
+        <v>1689</v>
       </c>
       <c r="I58" s="8">
-        <v>10</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>116</v>
+        <v>4</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L58" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -3599,1767 +3507,1677 @@
         <v>27</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C59" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>92</v>
+        <v>54</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="7">
-        <v>1206</v>
+        <v>1689</v>
       </c>
       <c r="I59" s="8">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="J59" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K59" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L59" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B60" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C60" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>92</v>
+      <c r="B60" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="7">
-        <v>1206</v>
+        <v>1689</v>
       </c>
       <c r="I60" s="8">
-        <v>5</v>
-      </c>
-      <c r="J60" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K60" s="7" t="s">
-        <v>105</v>
+        <v>195</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L60" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="12" t="s">
-        <v>27</v>
+      <c r="A61" s="8" t="s">
+        <v>22</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D61" s="8" t="s">
-        <v>92</v>
+        <v>49</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="7">
-        <v>1206</v>
-      </c>
-      <c r="I61" s="12">
-        <v>20</v>
-      </c>
-      <c r="J61" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="K61" s="13" t="s">
-        <v>116</v>
+        <v>1930</v>
+      </c>
+      <c r="I61" s="8">
+        <v>1</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L61" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="B62" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>110</v>
+        <v>22</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="7">
-        <v>1206</v>
+        <v>1930</v>
       </c>
       <c r="I62" s="8">
-        <v>3</v>
-      </c>
-      <c r="J62" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="K62" s="13" t="s">
-        <v>118</v>
+        <v>2</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L62" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="7">
-        <v>1206</v>
+        <v>1930</v>
       </c>
       <c r="I63" s="8">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L63" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>68</v>
+        <v>50</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="7">
-        <v>1689</v>
+        <v>1930</v>
       </c>
       <c r="I64" s="8">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L64" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="8" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C65" s="8" t="s">
-        <v>110</v>
+        <v>50</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="7">
-        <v>1689</v>
+        <v>1930</v>
       </c>
       <c r="I65" s="8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J65" s="7" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="L65" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="7">
-        <v>1689</v>
+        <v>1930</v>
       </c>
       <c r="I66" s="8">
-        <v>195</v>
+        <v>52</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L66" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C67" s="8" t="s">
-        <v>68</v>
+        <v>39</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="7">
-        <v>1930</v>
+        <v>1206</v>
       </c>
       <c r="I67" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J67" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K67" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L67" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>89</v>
+        <v>39</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="7">
-        <v>1930</v>
+        <v>1206</v>
       </c>
       <c r="I68" s="8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J68" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K68" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L68" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>51</v>
+      <c r="A69" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>39</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>89</v>
+        <v>107</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>84</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="7">
-        <v>1930</v>
+        <v>1206</v>
       </c>
       <c r="I69" s="8">
-        <v>13</v>
-      </c>
-      <c r="J69" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>116</v>
+        <v>41</v>
+      </c>
+      <c r="J69" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K69" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L69" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D70" s="7" t="s">
+      <c r="A70" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D70" s="4" t="s">
         <v>84</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="7">
-        <v>1930</v>
+        <v>1206</v>
       </c>
       <c r="I70" s="8">
-        <v>12</v>
-      </c>
-      <c r="J70" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K70" s="7" t="s">
-        <v>70</v>
+        <v>358</v>
+      </c>
+      <c r="J70" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L70" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C71" s="8" t="s">
-        <v>110</v>
+        <v>12</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>84</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="7">
-        <v>1930</v>
+        <v>1206</v>
       </c>
       <c r="I71" s="8">
-        <v>9</v>
-      </c>
-      <c r="J71" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K71" s="7" t="s">
-        <v>105</v>
+        <v>2</v>
+      </c>
+      <c r="J71" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="K71" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="L71" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>52</v>
+      <c r="A72" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>84</v>
+        <v>107</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="7">
-        <v>1930</v>
-      </c>
-      <c r="I72" s="8">
-        <v>52</v>
+        <v>1086</v>
+      </c>
+      <c r="I72" s="10">
+        <v>30</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>116</v>
+        <v>143</v>
+      </c>
+      <c r="K72" s="11" t="s">
+        <v>112</v>
       </c>
       <c r="L72" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="8" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>68</v>
+        <v>56</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="7">
-        <v>1206</v>
+        <v>1086</v>
       </c>
       <c r="I73" s="8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J73" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L73" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C74" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>87</v>
+        <v>56</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>91</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="7">
-        <v>1206</v>
+        <v>1086</v>
       </c>
       <c r="I74" s="8">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J74" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K74" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L74" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C75" s="8" t="s">
-        <v>110</v>
+        <v>29</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="7">
-        <v>1206</v>
+        <v>1086</v>
       </c>
       <c r="I75" s="8">
-        <v>41</v>
-      </c>
-      <c r="J75" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K75" s="7" t="s">
-        <v>105</v>
+        <v>4</v>
+      </c>
+      <c r="J75" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="K75" s="11" t="s">
+        <v>114</v>
       </c>
       <c r="L75" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>87</v>
+        <v>107</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="7">
-        <v>1206</v>
+        <v>1086</v>
       </c>
       <c r="I76" s="8">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K76" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L76" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="B77" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C77" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D77" s="8" t="s">
-        <v>87</v>
+        <v>38</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="7">
-        <v>1206</v>
+        <v>823</v>
       </c>
       <c r="I77" s="8">
-        <v>2</v>
-      </c>
-      <c r="J77" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="K77" s="13" t="s">
-        <v>118</v>
+        <v>3</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L77" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="12" t="s">
-        <v>30</v>
+      <c r="A78" s="8" t="s">
+        <v>38</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C78" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>94</v>
+        <v>65</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>92</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="7">
-        <v>1086</v>
-      </c>
-      <c r="I78" s="12">
-        <v>30</v>
-      </c>
-      <c r="J78" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="K78" s="13" t="s">
-        <v>116</v>
+        <v>823</v>
+      </c>
+      <c r="I78" s="8">
+        <v>0</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K78" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L78" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B79" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C79" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>94</v>
+      <c r="A79" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="7">
-        <v>1086</v>
+        <v>823</v>
       </c>
       <c r="I79" s="8">
-        <v>7</v>
-      </c>
-      <c r="J79" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K79" s="7" t="s">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L79" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="8" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C80" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>94</v>
+        <v>64</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="7">
-        <v>1086</v>
+        <v>921</v>
       </c>
       <c r="I80" s="8">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K80" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L80" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B81" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C81" s="8" t="s">
-        <v>110</v>
+        <v>37</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="7">
-        <v>1086</v>
+        <v>921</v>
       </c>
       <c r="I81" s="8">
-        <v>4</v>
-      </c>
-      <c r="J81" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="K81" s="13" t="s">
-        <v>118</v>
+        <v>30</v>
+      </c>
+      <c r="J81" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K81" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L81" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>94</v>
+        <v>107</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="7">
-        <v>1086</v>
+        <v>921</v>
       </c>
       <c r="I82" s="8">
-        <v>357</v>
+        <v>94</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L82" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C83" s="8" t="s">
-        <v>68</v>
+        <v>42</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D83" s="7" t="s">
         <v>95</v>
       </c>
       <c r="E83" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F83" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>146</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="7">
-        <v>823</v>
+        <v>2412</v>
       </c>
       <c r="I83" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J83" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K83" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L83" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C84" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D84" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D84" s="7" t="s">
         <v>95</v>
       </c>
       <c r="E84" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F84" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>146</v>
       </c>
       <c r="G84" s="7"/>
       <c r="H84" s="7">
-        <v>823</v>
+        <v>2412</v>
       </c>
       <c r="I84" s="8">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J84" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K84" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L84" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>67</v>
+      <c r="A85" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D85" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D85" s="8" t="s">
         <v>95</v>
       </c>
       <c r="E85" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F85" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>146</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="7">
-        <v>823</v>
+        <v>2412</v>
       </c>
       <c r="I85" s="8">
-        <v>1</v>
-      </c>
-      <c r="J85" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K85" s="3" t="s">
-        <v>116</v>
+        <v>8</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K85" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L85" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B86" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C86" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>77</v>
+      <c r="A86" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="E86" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F86" s="7" t="s">
         <v>124</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>143</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="7">
-        <v>921</v>
+        <v>2412</v>
       </c>
       <c r="I86" s="8">
-        <v>39</v>
-      </c>
-      <c r="J86" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K86" s="7" t="s">
-        <v>70</v>
+        <v>11</v>
+      </c>
+      <c r="J86" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L86" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="8" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="C87" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D87" s="8" t="s">
-        <v>77</v>
+        <v>61</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="7">
-        <v>921</v>
+        <v>3491</v>
       </c>
       <c r="I87" s="8">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="J87" s="7" t="s">
-        <v>152</v>
+        <v>66</v>
       </c>
       <c r="K87" s="7" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="L87" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>66</v>
+      <c r="A88" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>61</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>77</v>
+        <v>107</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="7">
-        <v>921</v>
-      </c>
-      <c r="I88" s="8">
-        <v>94</v>
-      </c>
-      <c r="J88" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K88" s="3" t="s">
-        <v>116</v>
+        <v>3491</v>
+      </c>
+      <c r="I88" s="8"/>
+      <c r="J88" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="K88" s="7" t="s">
+        <v>102</v>
       </c>
       <c r="L88" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D89" s="14" t="s">
-        <v>77</v>
+        <v>107</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="7">
-        <v>921</v>
-      </c>
-      <c r="I89" s="10">
-        <v>256</v>
+        <v>3491</v>
+      </c>
+      <c r="I89" s="8">
+        <v>2</v>
       </c>
       <c r="J89" s="9" t="s">
-        <v>121</v>
-      </c>
-      <c r="K89" s="11" t="s">
-        <v>120</v>
+        <v>142</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L89" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C90" s="8" t="s">
-        <v>68</v>
+        <v>47</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D90" s="7" t="s">
         <v>98</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="7">
-        <v>2412</v>
+        <v>1448</v>
       </c>
       <c r="I90" s="8">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J90" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K90" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L90" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="8" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C91" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D91" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D91" s="8" t="s">
         <v>98</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="7">
-        <v>2412</v>
+        <v>1448</v>
       </c>
       <c r="I91" s="8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J91" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K91" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L91" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C92" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D92" s="8" t="s">
+      <c r="A92" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D92" s="6" t="s">
         <v>98</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="7">
-        <v>2412</v>
+        <v>1448</v>
       </c>
       <c r="I92" s="8">
-        <v>8</v>
-      </c>
-      <c r="J92" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K92" s="7" t="s">
-        <v>105</v>
+        <v>4</v>
+      </c>
+      <c r="J92" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K92" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L92" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>43</v>
+      <c r="A93" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>98</v>
+        <v>107</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>87</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="7">
-        <v>2412</v>
+        <v>965</v>
       </c>
       <c r="I93" s="8">
-        <v>11</v>
-      </c>
-      <c r="J93" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K93" s="3" t="s">
-        <v>116</v>
+        <v>63</v>
+      </c>
+      <c r="J93" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K93" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L93" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C94" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>81</v>
+        <v>60</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>87</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="7">
-        <v>3491</v>
+        <v>965</v>
       </c>
       <c r="I94" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J94" s="7" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K94" s="7" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="L94" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C95" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>81</v>
+      <c r="A95" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="7">
-        <v>3491</v>
-      </c>
-      <c r="I95" s="8"/>
-      <c r="J95" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K95" s="7" t="s">
-        <v>105</v>
+        <v>965</v>
+      </c>
+      <c r="I95" s="8">
+        <v>20</v>
+      </c>
+      <c r="J95" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K95" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L95" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B96" s="4" t="s">
+      <c r="A96" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B96" s="8" t="s">
         <v>63</v>
       </c>
       <c r="C96" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D96" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D96" s="6" t="s">
-        <v>81</v>
-      </c>
       <c r="E96" s="7" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="7">
-        <v>3491</v>
+        <v>1397</v>
       </c>
       <c r="I96" s="8">
-        <v>2</v>
-      </c>
-      <c r="J96" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>116</v>
+        <v>7</v>
+      </c>
+      <c r="J96" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K96" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="L96" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B97" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C97" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>101</v>
+      <c r="A97" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="7">
-        <v>1448</v>
+        <v>1397</v>
       </c>
       <c r="I97" s="8">
-        <v>15</v>
-      </c>
-      <c r="J97" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K97" s="7" t="s">
-        <v>70</v>
+        <v>8</v>
+      </c>
+      <c r="J97" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>112</v>
       </c>
       <c r="L97" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I98" s="1">
+        <v>240</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L98" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I99" s="1">
+        <v>150</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L99" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I100" s="1">
+        <v>204</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L100" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="I101" s="1">
+        <v>1026</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L101" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I102" s="1">
+        <v>504</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L102" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I103" s="1">
+        <v>30</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="L103" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B98" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C98" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G98" s="7"/>
-      <c r="H98" s="7">
-        <v>1448</v>
-      </c>
-      <c r="I98" s="8">
-        <v>0</v>
-      </c>
-      <c r="J98" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K98" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="L98" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G99" s="7"/>
-      <c r="H99" s="7">
-        <v>1448</v>
-      </c>
-      <c r="I99" s="8">
-        <v>4</v>
-      </c>
-      <c r="J99" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K99" s="3" t="s">
+      <c r="B104" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I104" s="1">
+        <v>80</v>
+      </c>
+      <c r="J104" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K104" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L99" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D100" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E100" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G100" s="7"/>
-      <c r="H100" s="7">
-        <v>1448</v>
-      </c>
-      <c r="I100" s="10">
-        <v>150</v>
-      </c>
-      <c r="J100" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="K100" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="L100" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B101" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C101" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G101" s="7"/>
-      <c r="H101" s="7">
-        <v>965</v>
-      </c>
-      <c r="I101" s="8">
-        <v>63</v>
-      </c>
-      <c r="J101" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K101" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L101" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B102" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="C102" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="D102" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G102" s="7"/>
-      <c r="H102" s="7">
-        <v>965</v>
-      </c>
-      <c r="I102" s="8">
-        <v>5</v>
-      </c>
-      <c r="J102" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="K102" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="L102" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B103" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D103" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E103" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="G103" s="7"/>
-      <c r="H103" s="7">
-        <v>965</v>
-      </c>
-      <c r="I103" s="8">
-        <v>20</v>
-      </c>
-      <c r="J103" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K103" s="3" t="s">
+      <c r="L104" s="7" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I105" s="1">
+        <v>256</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="K105" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="L103" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B104" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C104" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E104" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F104" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="G104" s="7"/>
-      <c r="H104" s="7">
-        <v>1397</v>
-      </c>
-      <c r="I104" s="8">
-        <v>7</v>
-      </c>
-      <c r="J104" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="K104" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="L104" s="7" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B105" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E105" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="G105" s="7"/>
-      <c r="H105" s="7">
-        <v>1397</v>
-      </c>
-      <c r="I105" s="8">
-        <v>8</v>
-      </c>
-      <c r="J105" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="K105" s="3" t="s">
-        <v>116</v>
-      </c>
       <c r="L105" s="7" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L105" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="47" priority="856"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="856"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D18">
-    <cfRule type="duplicateValues" dxfId="46" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="158" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="159" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D11:D14">
+    <cfRule type="duplicateValues" dxfId="41" priority="977"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="978"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="979" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="980" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="981" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D19">
-    <cfRule type="duplicateValues" dxfId="38" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="150" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="151" stopIfTrue="1"/>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="duplicateValues" dxfId="36" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="158" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="159" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16">
+    <cfRule type="duplicateValues" dxfId="28" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="150" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="151" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:D18">
+    <cfRule type="duplicateValues" dxfId="20" priority="932"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="933"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="934"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="935"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="936"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="937"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="938" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="939" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="30" priority="906"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="907" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="988"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="989" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="28" priority="854"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="855" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="855" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="26" priority="852"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="853" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="853" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A100:A105">
-    <cfRule type="duplicateValues" dxfId="24" priority="930"/>
+  <conditionalFormatting sqref="A93:A97">
+    <cfRule type="duplicateValues" dxfId="6" priority="990"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A24 A9:A19">
-    <cfRule type="duplicateValues" dxfId="23" priority="931"/>
+  <conditionalFormatting sqref="D8:D10">
+    <cfRule type="duplicateValues" dxfId="5" priority="992"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="993" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="994"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="995" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="996" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D20:D21">
-    <cfRule type="duplicateValues" dxfId="22" priority="932"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="933"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="934"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="935"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="936"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="937"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="938" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="939" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D17">
-    <cfRule type="duplicateValues" dxfId="14" priority="953"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="954"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="955" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="956" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="957" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D13:D16">
-    <cfRule type="duplicateValues" dxfId="9" priority="977"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="978"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="979" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="980" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="981" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D12">
-    <cfRule type="duplicateValues" dxfId="4" priority="983"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="984" stopIfTrue="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="985"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="986" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9:D12">
-    <cfRule type="duplicateValues" dxfId="0" priority="987" stopIfTrue="1"/>
+  <conditionalFormatting sqref="A8:A16">
+    <cfRule type="duplicateValues" dxfId="0" priority="997"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 19\Tonor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\AM - Inventory replenishment\AM_Replenishment\data\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072C4DDC-9E02-4CD7-8FFC-2B36F4ADA122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7D5BB9C-5F28-4349-B1C3-21BEF33A3276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$97</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$100</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1695,7 +1695,7 @@
         <v>91</v>
       </c>
       <c r="I33">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J33" s="1" t="s">
         <v>101</v>
@@ -1715,7 +1715,7 @@
         <v>99</v>
       </c>
       <c r="I34">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="J34" s="1" t="s">
         <v>101</v>
@@ -1735,7 +1735,7 @@
         <v>72</v>
       </c>
       <c r="I35">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J35" s="1" t="s">
         <v>101</v>
@@ -1755,7 +1755,7 @@
         <v>83</v>
       </c>
       <c r="I36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J36" s="1" t="s">
         <v>101</v>
@@ -1775,7 +1775,7 @@
         <v>75</v>
       </c>
       <c r="I37">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J37" s="1" t="s">
         <v>101</v>
@@ -1795,7 +1795,7 @@
         <v>76</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J38" s="1" t="s">
         <v>101</v>
@@ -1855,7 +1855,7 @@
         <v>80</v>
       </c>
       <c r="I41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J41" s="1" t="s">
         <v>101</v>
@@ -1874,7 +1874,9 @@
       <c r="D42" t="s">
         <v>118</v>
       </c>
-      <c r="I42"/>
+      <c r="I42">
+        <v>0</v>
+      </c>
       <c r="J42" s="1" t="s">
         <v>101</v>
       </c>
@@ -1892,7 +1894,9 @@
       <c r="D43" t="s">
         <v>74</v>
       </c>
-      <c r="I43"/>
+      <c r="I43">
+        <v>1</v>
+      </c>
       <c r="J43" s="1" t="s">
         <v>101</v>
       </c>
@@ -1910,7 +1914,9 @@
       <c r="D44" t="s">
         <v>73</v>
       </c>
-      <c r="I44"/>
+      <c r="I44">
+        <v>0</v>
+      </c>
       <c r="J44" s="1" t="s">
         <v>101</v>
       </c>
@@ -1929,7 +1935,7 @@
         <v>93</v>
       </c>
       <c r="I45">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>101</v>
@@ -1989,7 +1995,7 @@
         <v>71</v>
       </c>
       <c r="I48">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J48" s="1" t="s">
         <v>101</v>
@@ -2028,7 +2034,9 @@
       <c r="D50" t="s">
         <v>78</v>
       </c>
-      <c r="I50"/>
+      <c r="I50">
+        <v>0</v>
+      </c>
       <c r="J50" s="1" t="s">
         <v>101</v>
       </c>
@@ -2067,7 +2075,7 @@
         <v>94</v>
       </c>
       <c r="I52">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>101</v>
@@ -2087,7 +2095,7 @@
         <v>92</v>
       </c>
       <c r="I53">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>101</v>
@@ -2107,7 +2115,7 @@
         <v>77</v>
       </c>
       <c r="I54">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>101</v>
@@ -2126,7 +2134,9 @@
       <c r="D55" t="s">
         <v>90</v>
       </c>
-      <c r="I55"/>
+      <c r="I55">
+        <v>0</v>
+      </c>
       <c r="J55" s="1" t="s">
         <v>101</v>
       </c>
@@ -2165,7 +2175,7 @@
         <v>97</v>
       </c>
       <c r="I57">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>101</v>
@@ -3035,7 +3045,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L97" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A59">
     <cfRule type="duplicateValues" dxfId="10" priority="11"/>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 24\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0D94B79-BCAB-4B79-871F-A30F400B3906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750A2661-0B72-4D09-A3C0-D7533A561E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="77">
   <si>
     <t>SKU</t>
   </si>
@@ -258,21 +258,23 @@
     <t>Pipeline</t>
   </si>
   <si>
-    <t>In-Transit Inventory</t>
-  </si>
-  <si>
     <t>Open Order</t>
+  </si>
+  <si>
+    <t>T30</t>
+  </si>
+  <si>
+    <t>TD310+</t>
+  </si>
+  <si>
+    <t>TC-2030</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -311,18 +313,6 @@
       <color theme="1"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111827"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1F2937"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -369,13 +359,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -395,42 +384,13 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Comma" xfId="3" builtinId="3"/>
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{697FC575-8A7C-4715-A8F0-2950C62D8576}"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="12">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1953,103 +1913,88 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I47" s="9">
+      <c r="C47" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I47" s="1">
         <v>30</v>
       </c>
-      <c r="J47" s="7" t="s">
+      <c r="J47" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="K47" s="8" t="s">
+    </row>
+    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I48" s="1">
+        <v>256</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I49" s="1">
+        <v>80</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I48" s="9">
-        <v>256</v>
-      </c>
-      <c r="J48" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="K48" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I49" s="10">
-        <v>80</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="K49" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A26:A44">
+    <cfRule type="duplicateValues" dxfId="9" priority="2165"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A35">
-    <cfRule type="duplicateValues" dxfId="11" priority="2133"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="2134"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A49">
-    <cfRule type="duplicateValues" dxfId="9" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2133"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2134"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="1894"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1894"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="7" priority="2105"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2105"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2106" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="5" priority="1892"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1893" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1892"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1893" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="3" priority="1890"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1891" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A47:A48">
-    <cfRule type="duplicateValues" dxfId="1" priority="2162"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26:A44">
-    <cfRule type="duplicateValues" dxfId="0" priority="2165"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1890"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1891" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 24\Tonor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 25\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750A2661-0B72-4D09-A3C0-D7533A561E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A55FD4-D1E4-4E29-B073-73D9C2755E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$63</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="89">
   <si>
     <t>SKU</t>
   </si>
@@ -111,6 +111,9 @@
     <t>FBA77117</t>
   </si>
   <si>
+    <t>FBA79112</t>
+  </si>
+  <si>
     <t>FBA79113</t>
   </si>
   <si>
@@ -180,6 +183,9 @@
     <t>B078WNW4YW</t>
   </si>
   <si>
+    <t>B0BRKDLXCD</t>
+  </si>
+  <si>
     <t>B0BTCXQQ6M</t>
   </si>
   <si>
@@ -228,7 +234,19 @@
     <t>B0BVHZ5MKZ</t>
   </si>
   <si>
-    <t>Week 24</t>
+    <t>Tonor</t>
+  </si>
+  <si>
+    <t>FBA77114</t>
+  </si>
+  <si>
+    <t>B07TSN2H9D</t>
+  </si>
+  <si>
+    <t>In-Transit Inventory</t>
+  </si>
+  <si>
+    <t>Open Order</t>
   </si>
   <si>
     <t>AMPM</t>
@@ -237,44 +255,66 @@
     <t>Warehouse</t>
   </si>
   <si>
-    <t>Tonor</t>
-  </si>
-  <si>
-    <t>FBA77114</t>
-  </si>
-  <si>
-    <t>B07TSN2H9D</t>
+    <t>B07JMYG6LF</t>
+  </si>
+  <si>
+    <t>FBA77100</t>
+  </si>
+  <si>
+    <t>B083LPYPS9</t>
+  </si>
+  <si>
+    <t>FBA77112</t>
+  </si>
+  <si>
+    <t>B0C4LRZ9ZZ</t>
+  </si>
+  <si>
+    <t>FBA78924</t>
+  </si>
+  <si>
+    <t>B0C8JDHLX9</t>
+  </si>
+  <si>
+    <t>FBA79115</t>
+  </si>
+  <si>
+    <t>B0BG8CJXHH</t>
+  </si>
+  <si>
+    <t>FBA79575</t>
+  </si>
+  <si>
+    <t>B0CFKZ72N7</t>
+  </si>
+  <si>
+    <t>FBA79578</t>
+  </si>
+  <si>
+    <t>B0CQX4GVSB</t>
+  </si>
+  <si>
+    <t>FBA79579</t>
+  </si>
+  <si>
+    <t>B0CCVBQRFX</t>
   </si>
   <si>
     <t>FBA79582</t>
   </si>
   <si>
-    <t>B0CCVBQRFX</t>
-  </si>
-  <si>
     <t>B2B - AMPM</t>
-  </si>
-  <si>
-    <t>Pipeline</t>
-  </si>
-  <si>
-    <t>Open Order</t>
-  </si>
-  <si>
-    <t>T30</t>
-  </si>
-  <si>
-    <t>TD310+</t>
-  </si>
-  <si>
-    <t>TC-2030</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,6 +353,18 @@
       <color theme="1"/>
       <name val="Bookman Old Style"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2937"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -359,12 +411,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -381,16 +434,44 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Comma" xfId="3" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="2" xr:uid="{697FC575-8A7C-4715-A8F0-2950C62D8576}"/>
     <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="12">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -821,7 +902,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -879,1122 +960,1273 @@
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
         <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I5">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I6">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
         <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I7">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I8">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I9">
-        <v>139</v>
+        <v>4</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>138</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
         <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I11">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
         <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I12">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" t="s">
+        <v>60</v>
+      </c>
+      <c r="I13">
         <v>38</v>
       </c>
-      <c r="C13" t="s">
-        <v>58</v>
-      </c>
-      <c r="I13">
-        <v>11</v>
-      </c>
       <c r="J13" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
         <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I15">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
         <v>49</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I16">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I17">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
         <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I18">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
         <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I19">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
         <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I20">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
         <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I21">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
         <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I22">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B23" t="s">
         <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I23">
-        <v>99</v>
+        <v>7</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
         <v>57</v>
       </c>
       <c r="C24" t="s">
+        <v>60</v>
+      </c>
+      <c r="I24">
+        <v>6</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" t="s">
         <v>58</v>
       </c>
-      <c r="I24">
+      <c r="C25" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25">
+        <v>39</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" t="s">
+        <v>60</v>
+      </c>
+      <c r="I26">
+        <v>37</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" t="s">
+        <v>60</v>
+      </c>
+      <c r="I27">
+        <v>31</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I28" s="8">
+        <v>80</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="C30" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I30" s="3">
+        <v>331</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I31" s="3">
+        <v>34</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I33" s="3">
+        <v>30</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I35" s="3">
+        <v>33</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I36" s="3">
+        <v>104</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I37" s="3">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I38" s="3">
+        <v>6</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I39" s="3">
+        <v>49</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I40" s="3">
+        <v>130</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I41" s="3">
+        <v>552</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I42" s="3">
+        <v>10</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I45" s="3">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I46" s="3">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I47" s="3">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I48" s="3">
+        <v>99</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I50" s="3">
+        <v>164</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I51" s="3">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I52" s="3">
+        <v>11</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I53" s="3">
+        <v>15</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I54" s="3">
+        <v>0</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I55" s="3">
+        <v>0</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I56" s="3">
+        <v>5</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I58" s="3">
+        <v>30</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I59" s="3">
+        <v>21</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="C60" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I60" s="3">
+        <v>323</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B61" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="I25">
-        <v>31</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+      <c r="C61" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="I61" s="3">
+        <v>295</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I62" s="9">
+        <v>3</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I26" s="3">
-        <v>331</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I27" s="3">
-        <v>42</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I28" s="3">
-        <v>38</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="4" t="s">
+      <c r="B63" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I29" s="3">
-        <v>104</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I30" s="3">
-        <v>6</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I31" s="3">
-        <v>49</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I32" s="3">
-        <v>130</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I33" s="3">
-        <v>572</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I34" s="3">
-        <v>10</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I35" s="3">
-        <v>106</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I36" s="3">
-        <v>183</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I37" s="3">
-        <v>11</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I38" s="3">
-        <v>16</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I39" s="3">
-        <v>5</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I40" s="3">
-        <v>1</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I41" s="3">
-        <v>30</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I42" s="3">
-        <v>28</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I43" s="3">
-        <v>329</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I44" s="3">
-        <v>43</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I45" s="6">
-        <v>3</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="I46" s="6">
+      <c r="C63" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="I63" s="9">
         <v>2</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="I47" s="1">
-        <v>30</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I48" s="1">
-        <v>256</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I49" s="1">
-        <v>80</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>73</v>
+      <c r="J63" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A26:A44">
-    <cfRule type="duplicateValues" dxfId="9" priority="2165"/>
+  <conditionalFormatting sqref="A29">
+    <cfRule type="duplicateValues" dxfId="11" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A35">
-    <cfRule type="duplicateValues" dxfId="8" priority="2133"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2134"/>
+  <conditionalFormatting sqref="A47:A49">
+    <cfRule type="duplicateValues" dxfId="10" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="6" priority="1894"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="1917"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="5" priority="2105"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2106" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2128"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2129" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="3" priority="1892"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="1893" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1915"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1916" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="1" priority="1890"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="1891" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1913"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1914" stopIfTrue="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29:A61">
+    <cfRule type="duplicateValues" dxfId="1" priority="2136"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A28">
+    <cfRule type="duplicateValues" dxfId="0" priority="2137"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 28\Tonor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 29\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B06AAF56-FFFE-4664-A2F1-59E842BD45EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC618F1-7A24-469F-AF87-70B92EF9EF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="76">
   <si>
     <t>SKU</t>
   </si>
@@ -90,9 +90,6 @@
     <t>FBA77105</t>
   </si>
   <si>
-    <t>FBA77110</t>
-  </si>
-  <si>
     <t>FBA77115</t>
   </si>
   <si>
@@ -150,9 +147,6 @@
     <t>B089FVQD3Z</t>
   </si>
   <si>
-    <t>B08NDB5NWP</t>
-  </si>
-  <si>
     <t>B08V1JS3NY</t>
   </si>
   <si>
@@ -220,9 +214,6 @@
   </si>
   <si>
     <t>T30</t>
-  </si>
-  <si>
-    <t>TM20</t>
   </si>
   <si>
     <t>TC30</t>
@@ -248,6 +239,9 @@
 ORCA001</t>
   </si>
   <si>
+    <t xml:space="preserve">TC310	</t>
+  </si>
+  <si>
     <t>TC310+</t>
   </si>
   <si>
@@ -273,9 +267,6 @@
   </si>
   <si>
     <t>TD310+</t>
-  </si>
-  <si>
-    <t>TC310</t>
   </si>
 </sst>
 </file>
@@ -286,7 +277,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,19 +324,13 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF1F2937"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -361,12 +346,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -409,6 +388,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -418,11 +400,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -431,10 +410,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -942,473 +921,472 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" s="3">
+        <v>306</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="3">
+        <v>6</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="3">
+        <v>6</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="12">
-        <v>306</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="C5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="3">
+        <v>104</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="3">
+        <v>6</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="3">
+        <v>49</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="3">
+        <v>130</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I9" s="3">
+        <v>523</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I10" s="3">
+        <v>10</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" s="3">
+        <v>81</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I12" s="3">
+        <v>71</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="3">
+        <v>7</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="3">
+        <v>10</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I15" s="3">
+        <v>5</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" s="12">
-        <v>6</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I4" s="12">
-        <v>4</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I5" s="12">
-        <v>1</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="12">
-        <v>105</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="I7" s="12">
-        <v>6</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="B16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I16" s="3">
+        <v>22</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17" s="3">
+        <v>7</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" s="3">
+        <v>302</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I19" s="3">
+        <v>260</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="I8" s="12">
-        <v>49</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="C20" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="I9" s="12">
-        <v>130</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I10" s="12">
-        <v>523</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" s="12">
-        <v>10</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="I20" s="9">
+        <v>2</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
         <v>22</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="I12" s="12">
-        <v>81</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="I13" s="12">
-        <v>71</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="I14" s="12">
-        <v>7</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" s="12">
-        <v>11</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" s="12">
-        <v>5</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="I17" s="12">
-        <v>26</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" s="12">
-        <v>13</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="I19" s="12">
-        <v>302</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="I20" s="12">
-        <v>259</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>41</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="I21" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
         <v>12</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I22" s="9">
         <v>2</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>52</v>
       </c>
+      <c r="C23" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="D23" s="11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="I23" s="7">
         <v>80</v>
       </c>
-      <c r="J23" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="K23" s="6"/>
+      <c r="J23" s="6" t="s">
+        <v>53</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L23" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="10" priority="2376"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="2377"/>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="duplicateValues" dxfId="10" priority="2484"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2485"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="2134"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="7" priority="2345"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2346" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2452"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2453" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="5" priority="2132"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2133" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2239"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2240" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="3" priority="2130"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2131" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2237"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2238" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="1" priority="2407"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2520"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A20">
-    <cfRule type="duplicateValues" dxfId="0" priority="2410"/>
+  <conditionalFormatting sqref="A2:A19">
+    <cfRule type="duplicateValues" dxfId="0" priority="2523"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 29\Tonor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 30\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCC618F1-7A24-469F-AF87-70B92EF9EF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C970EE-D438-4D6A-8933-D7F4E2CE446D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="79">
   <si>
     <t>SKU</t>
   </si>
@@ -84,6 +84,9 @@
     <t>FBA77113</t>
   </si>
   <si>
+    <t>FBA79111</t>
+  </si>
+  <si>
     <t>FBA77103</t>
   </si>
   <si>
@@ -139,6 +142,9 @@
   </si>
   <si>
     <t>B01ISNU3X4</t>
+  </si>
+  <si>
+    <t>B0BRKFP94K</t>
   </si>
   <si>
     <t>B09Z5Q194D</t>
@@ -237,6 +243,9 @@
   <si>
     <t xml:space="preserve">
 ORCA001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD510	</t>
   </si>
   <si>
     <t xml:space="preserve">TC310	</t>
@@ -864,7 +873,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -925,59 +934,59 @@
         <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I2" s="3">
-        <v>306</v>
+        <v>290</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I3" s="3">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I4" s="3">
         <v>6</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -985,79 +994,79 @@
         <v>13</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I5" s="3">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I6" s="3">
         <v>6</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="I7" s="3">
         <v>50</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="3">
-        <v>49</v>
-      </c>
       <c r="J7" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I8" s="3">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1065,328 +1074,368 @@
         <v>14</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I9" s="3">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="I10" s="3">
         <v>10</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I11" s="3">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I12" s="3">
-        <v>71</v>
+        <v>3</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I13" s="3">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I14" s="3">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I15" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" s="3">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I17" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I18" s="3">
-        <v>302</v>
+        <v>26</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>48</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I19" s="3">
+        <v>7</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I20" s="3">
+        <v>287</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19" s="3">
+      <c r="C21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I21" s="3">
         <v>260</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="I20" s="9">
-        <v>2</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="I21" s="9">
-        <v>4</v>
-      </c>
       <c r="J21" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I22" s="9">
         <v>2</v>
       </c>
       <c r="J22" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I23" s="9">
+        <v>4</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I24" s="9">
+        <v>2</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I25" s="7">
+        <v>80</v>
+      </c>
+      <c r="J25" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="I23" s="7">
-        <v>80</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:L23" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
+  <autoFilter ref="A1:L25" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="10" priority="2484"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="2485"/>
+  <conditionalFormatting sqref="A12:A13">
+    <cfRule type="duplicateValues" dxfId="10" priority="2603"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2604"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="2241"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="7" priority="2452"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2453" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2576"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2577" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="5" priority="2239"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2240" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2363"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2364" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="3" priority="2237"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2238" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2361"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2362" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="1" priority="2520"/>
+  <conditionalFormatting sqref="A25">
+    <cfRule type="duplicateValues" dxfId="1" priority="2639"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A19">
-    <cfRule type="duplicateValues" dxfId="0" priority="2523"/>
+  <conditionalFormatting sqref="A2:A21">
+    <cfRule type="duplicateValues" dxfId="0" priority="2642"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 30\Tonor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 31\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87C970EE-D438-4D6A-8933-D7F4E2CE446D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F00260-A3CE-48E1-84FC-6A2F924A0C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FFC2A7B7-9814-40EF-9366-0F59D71BB19E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -78,139 +78,130 @@
     <t>FBA77101</t>
   </si>
   <si>
+    <t>B07WLWN2ZT</t>
+  </si>
+  <si>
+    <t>FBA79260</t>
+  </si>
+  <si>
+    <t>B07GVGMW59</t>
+  </si>
+  <si>
+    <t>FBA77105</t>
+  </si>
+  <si>
+    <t>B089FVQD3Z</t>
+  </si>
+  <si>
     <t>FBA77111</t>
   </si>
   <si>
+    <t>B08CVP2HXP</t>
+  </si>
+  <si>
+    <t>FBA77114</t>
+  </si>
+  <si>
+    <t>B07TSN2H9D</t>
+  </si>
+  <si>
+    <t>FBA77115</t>
+  </si>
+  <si>
+    <t>B08V1JS3NY</t>
+  </si>
+  <si>
+    <t>FBA77116</t>
+  </si>
+  <si>
+    <t>B0BBL47VR5</t>
+  </si>
+  <si>
+    <t>FBA77117</t>
+  </si>
+  <si>
+    <t>B078WNW4YW</t>
+  </si>
+  <si>
     <t>FBA77113</t>
   </si>
   <si>
+    <t>B01ISNU3X4</t>
+  </si>
+  <si>
+    <t>FBA77103</t>
+  </si>
+  <si>
+    <t>B09Z5Q194D</t>
+  </si>
+  <si>
     <t>FBA79111</t>
   </si>
   <si>
-    <t>FBA77103</t>
-  </si>
-  <si>
-    <t>FBA77105</t>
-  </si>
-  <si>
-    <t>FBA77115</t>
-  </si>
-  <si>
-    <t>FBA77116</t>
-  </si>
-  <si>
-    <t>FBA77117</t>
+    <t>B0BRKFP94K</t>
   </si>
   <si>
     <t>FBA79113</t>
   </si>
   <si>
+    <t>B0BTCXQQ6M</t>
+  </si>
+  <si>
     <t>FBA79114</t>
   </si>
   <si>
+    <t>B0CCV74CL7</t>
+  </si>
+  <si>
     <t>FBA79116</t>
   </si>
   <si>
-    <t>FBA79260</t>
+    <t>B0BYHHSLPC</t>
+  </si>
+  <si>
+    <t>FBA79576</t>
+  </si>
+  <si>
+    <t>B0BRCR2QQ7</t>
+  </si>
+  <si>
+    <t>FBA79577</t>
+  </si>
+  <si>
+    <t>B0CSCT63BL</t>
+  </si>
+  <si>
+    <t>FBA79586</t>
+  </si>
+  <si>
+    <t>B0CH9JR3HL</t>
   </si>
   <si>
     <t>FBA79574</t>
   </si>
   <si>
-    <t>FBA79576</t>
-  </si>
-  <si>
-    <t>FBA79577</t>
+    <t>B0B4WTHLX5</t>
   </si>
   <si>
     <t>FBA79585</t>
   </si>
   <si>
-    <t>FBA79586</t>
+    <t>B0CFKHCQ8W</t>
+  </si>
+  <si>
+    <t>FBA79697</t>
+  </si>
+  <si>
+    <t>B0CQX4K9P5</t>
   </si>
   <si>
     <t>FBA79696</t>
   </si>
   <si>
-    <t>FBA79697</t>
-  </si>
-  <si>
-    <t>B07WLWN2ZT</t>
-  </si>
-  <si>
-    <t>B08CVP2HXP</t>
-  </si>
-  <si>
-    <t>B01ISNU3X4</t>
-  </si>
-  <si>
-    <t>B0BRKFP94K</t>
-  </si>
-  <si>
-    <t>B09Z5Q194D</t>
-  </si>
-  <si>
-    <t>B089FVQD3Z</t>
-  </si>
-  <si>
-    <t>B08V1JS3NY</t>
-  </si>
-  <si>
-    <t>B0BBL47VR5</t>
-  </si>
-  <si>
-    <t>B078WNW4YW</t>
-  </si>
-  <si>
-    <t>B0BTCXQQ6M</t>
-  </si>
-  <si>
-    <t>B0CCV74CL7</t>
-  </si>
-  <si>
-    <t>B0BYHHSLPC</t>
-  </si>
-  <si>
-    <t>B07GVGMW59</t>
-  </si>
-  <si>
-    <t>B0B4WTHLX5</t>
-  </si>
-  <si>
-    <t>B0BRCR2QQ7</t>
-  </si>
-  <si>
-    <t>B0CSCT63BL</t>
-  </si>
-  <si>
-    <t>B0CFKHCQ8W</t>
-  </si>
-  <si>
-    <t>B0CH9JR3HL</t>
-  </si>
-  <si>
     <t>B0CQX3VB1R</t>
   </si>
   <si>
-    <t>B0CQX4K9P5</t>
-  </si>
-  <si>
     <t>Tonor</t>
-  </si>
-  <si>
-    <t>FBA77114</t>
-  </si>
-  <si>
-    <t>B07TSN2H9D</t>
-  </si>
-  <si>
-    <t>Open Order</t>
-  </si>
-  <si>
-    <t>AMPM</t>
-  </si>
-  <si>
-    <t>B2B - AMPM</t>
   </si>
   <si>
     <t>TC-777</t>
@@ -276,6 +267,15 @@
   </si>
   <si>
     <t>TD310+</t>
+  </si>
+  <si>
+    <t>AMPM</t>
+  </si>
+  <si>
+    <t>B2B - AMPM</t>
+  </si>
+  <si>
+    <t>Open Order</t>
   </si>
 </sst>
 </file>
@@ -283,21 +283,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -308,19 +301,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Bookman Old Style"/>
@@ -328,13 +308,27 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF111827"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF111827"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -385,66 +379,140 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="3" builtinId="3"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{697FC575-8A7C-4715-A8F0-2950C62D8576}"/>
-    <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{F37F9E33-BAB9-493A-9CBA-C25E5FEA33D0}"/>
+    <cellStyle name="Normal 6" xfId="2" xr:uid="{C0B7BEB6-A9CE-4FBD-8F7F-EC4AAD93DADA}"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -567,39 +635,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -651,7 +719,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -762,6 +830,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -770,13 +845,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -841,91 +909,56 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1E6F6A-7C3C-4952-AC4D-06F30C852840}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="23.33203125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="28.44140625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.44140625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -934,508 +967,499 @@
         <v>12</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>58</v>
+        <v>13</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="I2" s="3">
-        <v>290</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>56</v>
+        <v>286</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>59</v>
+        <v>15</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>56</v>
       </c>
       <c r="I3" s="3">
-        <v>60</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>56</v>
+        <v>14</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>60</v>
+      <c r="C4" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="I4" s="3">
-        <v>6</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>56</v>
+        <v>5</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>61</v>
+        <v>19</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="I5" s="3">
-        <v>69</v>
-      </c>
-      <c r="J5" s="1" t="s">
         <v>56</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>63</v>
+        <v>23</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="I6" s="3">
         <v>6</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>56</v>
+      <c r="J6" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>64</v>
+        <v>25</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="I7" s="3">
         <v>50</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>56</v>
+      <c r="J7" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>65</v>
+        <v>27</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="I8" s="3">
-        <v>118</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>56</v>
+        <v>115</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>66</v>
+        <v>29</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="I9" s="3">
-        <v>518</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>56</v>
+        <v>496</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>67</v>
+        <v>31</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="I10" s="3">
         <v>10</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>56</v>
+      <c r="J10" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>68</v>
+        <v>33</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="I11" s="3">
-        <v>7</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>56</v>
+        <v>6</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>69</v>
+        <v>35</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="I12" s="3">
         <v>3</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>56</v>
+      <c r="J12" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>70</v>
+        <v>37</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="I13" s="3">
-        <v>80</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>56</v>
+        <v>76</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" s="3">
         <v>71</v>
       </c>
-      <c r="I14" s="3">
-        <v>72</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>56</v>
+      <c r="J14" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>72</v>
+        <v>41</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>69</v>
       </c>
       <c r="I15" s="3">
         <v>8</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>56</v>
+      <c r="J15" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>73</v>
+        <v>43</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="I16" s="3">
-        <v>9</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>56</v>
+        <v>4</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>74</v>
+        <v>45</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="I17" s="3">
         <v>5</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>56</v>
+      <c r="J17" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>75</v>
+        <v>47</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>72</v>
       </c>
       <c r="I18" s="3">
         <v>26</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>56</v>
+      <c r="J18" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>76</v>
+        <v>49</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>73</v>
       </c>
       <c r="I19" s="3">
         <v>7</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>56</v>
+      <c r="J19" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>77</v>
+      <c r="C20" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>74</v>
       </c>
       <c r="I20" s="3">
         <v>287</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>56</v>
+      <c r="J20" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>78</v>
+        <v>53</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="I21" s="3">
-        <v>260</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>56</v>
+        <v>257</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="I22" s="9">
+      <c r="A22" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I22" s="8">
         <v>2</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>57</v>
+      <c r="J22" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="I23" s="9">
+      <c r="A23" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I23" s="8">
         <v>4</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>57</v>
+      <c r="J23" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="I24" s="9">
+      <c r="B24" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" s="8">
         <v>2</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>57</v>
+      <c r="J24" s="2" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I25" s="7">
+        <v>21</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I25" s="12">
         <v>80</v>
       </c>
-      <c r="J25" s="6" t="s">
-        <v>55</v>
+      <c r="J25" s="11" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L25" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A12:A13">
-    <cfRule type="duplicateValues" dxfId="10" priority="2603"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="2604"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="8" priority="2365"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="140"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="7" priority="2576"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="2577" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="142" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="5" priority="2363"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2364" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="139" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="3" priority="2361"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2362" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="137" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="1" priority="2639"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A21">
-    <cfRule type="duplicateValues" dxfId="0" priority="2642"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="144"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nitesh\Nitesh Gdrive\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 31\Tonor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive D\Week 32\Week 31 &amp; 32\Inventory\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F00260-A3CE-48E1-84FC-6A2F924A0C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66A4811-BDA6-4397-84CF-036A61080B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FFC2A7B7-9814-40EF-9366-0F59D71BB19E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -78,9 +78,48 @@
     <t>FBA77101</t>
   </si>
   <si>
+    <t>FBA79113</t>
+  </si>
+  <si>
+    <t>FBA79116</t>
+  </si>
+  <si>
     <t>B07WLWN2ZT</t>
   </si>
   <si>
+    <t>B0BTCXQQ6M</t>
+  </si>
+  <si>
+    <t>B0BYHHSLPC</t>
+  </si>
+  <si>
+    <t>Tonor</t>
+  </si>
+  <si>
+    <t>B2B - AMPM</t>
+  </si>
+  <si>
+    <t>TC-777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC310	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TC-777 PRO	</t>
+  </si>
+  <si>
+    <t>FBA77114</t>
+  </si>
+  <si>
+    <t>B07TSN2H9D</t>
+  </si>
+  <si>
+    <t>TC-2030</t>
+  </si>
+  <si>
+    <t>Open Order</t>
+  </si>
+  <si>
     <t>FBA79260</t>
   </si>
   <si>
@@ -99,12 +138,6 @@
     <t>B08CVP2HXP</t>
   </si>
   <si>
-    <t>FBA77114</t>
-  </si>
-  <si>
-    <t>B07TSN2H9D</t>
-  </si>
-  <si>
     <t>FBA77115</t>
   </si>
   <si>
@@ -141,24 +174,12 @@
     <t>B0BRKFP94K</t>
   </si>
   <si>
-    <t>FBA79113</t>
-  </si>
-  <si>
-    <t>B0BTCXQQ6M</t>
-  </si>
-  <si>
     <t>FBA79114</t>
   </si>
   <si>
     <t>B0CCV74CL7</t>
   </si>
   <si>
-    <t>FBA79116</t>
-  </si>
-  <si>
-    <t>B0BYHHSLPC</t>
-  </si>
-  <si>
     <t>FBA79576</t>
   </si>
   <si>
@@ -201,12 +222,6 @@
     <t>B0CQX3VB1R</t>
   </si>
   <si>
-    <t>Tonor</t>
-  </si>
-  <si>
-    <t>TC-777</t>
-  </si>
-  <si>
     <t>G11</t>
   </si>
   <si>
@@ -214,9 +229,6 @@
   </si>
   <si>
     <t>TC30</t>
-  </si>
-  <si>
-    <t>TC-2030</t>
   </si>
   <si>
     <t>TC40</t>
@@ -239,15 +251,9 @@
     <t xml:space="preserve">TD510	</t>
   </si>
   <si>
-    <t xml:space="preserve">TC310	</t>
-  </si>
-  <si>
     <t>TC310+</t>
   </si>
   <si>
-    <t xml:space="preserve">TC-777 PRO	</t>
-  </si>
-  <si>
     <t>TC30S+</t>
   </si>
   <si>
@@ -270,12 +276,6 @@
   </si>
   <si>
     <t>AMPM</t>
-  </si>
-  <si>
-    <t>B2B - AMPM</t>
-  </si>
-  <si>
-    <t>Open Order</t>
   </si>
 </sst>
 </file>
@@ -283,14 +283,21 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -301,6 +308,19 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Bookman Old Style"/>
@@ -308,27 +328,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF111827"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF111827"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -379,54 +385,54 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma" xfId="3" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="3" xr:uid="{F37F9E33-BAB9-493A-9CBA-C25E5FEA33D0}"/>
-    <cellStyle name="Normal 6" xfId="2" xr:uid="{C0B7BEB6-A9CE-4FBD-8F7F-EC4AAD93DADA}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{697FC575-8A7C-4715-A8F0-2950C62D8576}"/>
+    <cellStyle name="Normal 6" xfId="1" xr:uid="{E5F241CE-C0FC-4730-81C9-F1901EB82A3C}"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="11">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -439,80 +445,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -635,39 +567,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -719,7 +651,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -830,13 +762,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -845,6 +770,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -909,557 +841,600 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1E6F6A-7C3C-4952-AC4D-06F30C852840}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
   <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.88671875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="28.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="8.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" style="1" customWidth="1"/>
+    <col min="11" max="11" width="16.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="5">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="5">
+        <v>4</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="I2" s="3">
-        <v>286</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="I3" s="3">
-        <v>14</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="C4" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="I4" s="3">
-        <v>5</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>76</v>
+        <v>18</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="5">
+        <v>2</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="I5" s="3">
-        <v>56</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>76</v>
+        <v>24</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="11">
+        <v>80</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>60</v>
+        <v>15</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="I6" s="3">
-        <v>6</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>76</v>
+        <v>285</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>61</v>
       </c>
       <c r="I7" s="3">
-        <v>50</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>76</v>
+        <v>5</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>62</v>
       </c>
       <c r="I8" s="3">
-        <v>115</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>76</v>
+        <v>5</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>63</v>
       </c>
       <c r="I9" s="3">
-        <v>496</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>76</v>
+        <v>57</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="12" t="s">
         <v>64</v>
       </c>
       <c r="I10" s="3">
-        <v>10</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>76</v>
+        <v>6</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>65</v>
       </c>
       <c r="I11" s="3">
-        <v>6</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>76</v>
+        <v>50</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>66</v>
       </c>
       <c r="I12" s="3">
-        <v>3</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>76</v>
+        <v>115</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>67</v>
       </c>
       <c r="I13" s="3">
-        <v>76</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>76</v>
+        <v>473</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>68</v>
       </c>
       <c r="I14" s="3">
-        <v>71</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>76</v>
+        <v>10</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="12" t="s">
         <v>69</v>
       </c>
       <c r="I15" s="3">
-        <v>8</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>76</v>
+        <v>6</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>70</v>
+        <v>16</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="I16" s="3">
-        <v>4</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>76</v>
+        <v>2</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>71</v>
+        <v>46</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="I17" s="3">
-        <v>5</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>72</v>
+        <v>17</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>22</v>
       </c>
       <c r="I18" s="3">
-        <v>26</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>73</v>
+      <c r="C19" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="I19" s="3">
-        <v>7</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>76</v>
+        <v>8</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>74</v>
+      <c r="C20" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="I20" s="3">
-        <v>287</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>76</v>
+        <v>4</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" s="3">
+        <v>5</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="C22" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I22" s="3">
+        <v>26</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I21" s="3">
-        <v>257</v>
-      </c>
-      <c r="J21" s="2" t="s">
+      <c r="I23" s="3">
+        <v>7</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="I22" s="8">
-        <v>2</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="I23" s="8">
-        <v>4</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="I24" s="8">
-        <v>2</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>77</v>
+      <c r="I24" s="3">
+        <v>280</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="I25" s="12">
-        <v>80</v>
-      </c>
-      <c r="J25" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="I25" s="3">
+        <v>257</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>78</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="A5">
+    <cfRule type="duplicateValues" dxfId="10" priority="2700"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="15" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2480"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="6" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="142" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2691"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2692" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="4" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="139" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2478"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2479" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="2" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="137" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2476"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2477" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="144"/>
+  <conditionalFormatting sqref="A16:A17">
+    <cfRule type="duplicateValues" dxfId="2" priority="2704"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2705"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6:A25">
+    <cfRule type="duplicateValues" dxfId="0" priority="2712"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive D\Week 32\Week 31 &amp; 32\Inventory\Tonor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Drive D\Audio Array\Week 33\Week 33\Inventory\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E66A4811-BDA6-4397-84CF-036A61080B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FA9192-169D-42FF-B843-C230D65B96D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$22</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="73">
   <si>
     <t>SKU</t>
   </si>
@@ -75,191 +75,168 @@
     <t>Week</t>
   </si>
   <si>
+    <t>B2B - AMPM</t>
+  </si>
+  <si>
+    <t>Open Order</t>
+  </si>
+  <si>
+    <t>AMPM</t>
+  </si>
+  <si>
     <t>FBA77101</t>
   </si>
   <si>
+    <t>B07WLWN2ZT</t>
+  </si>
+  <si>
+    <t>FBA77105</t>
+  </si>
+  <si>
+    <t>B089FVQD3Z</t>
+  </si>
+  <si>
+    <t>FBA77111</t>
+  </si>
+  <si>
+    <t>B08CVP2HXP</t>
+  </si>
+  <si>
+    <t>FBA77114</t>
+  </si>
+  <si>
+    <t>B07TSN2H9D</t>
+  </si>
+  <si>
+    <t>FBA77115</t>
+  </si>
+  <si>
+    <t>B08V1JS3NY</t>
+  </si>
+  <si>
+    <t>FBA77116</t>
+  </si>
+  <si>
+    <t>B0BBL47VR5</t>
+  </si>
+  <si>
+    <t>FBA77117</t>
+  </si>
+  <si>
+    <t>B078WNW4YW</t>
+  </si>
+  <si>
+    <t>FBA77113</t>
+  </si>
+  <si>
+    <t>B01ISNU3X4</t>
+  </si>
+  <si>
+    <t>FBA77103</t>
+  </si>
+  <si>
+    <t>B09Z5Q194D</t>
+  </si>
+  <si>
+    <t>FBA79111</t>
+  </si>
+  <si>
+    <t>B0BRKFP94K</t>
+  </si>
+  <si>
     <t>FBA79113</t>
   </si>
   <si>
+    <t>B0BTCXQQ6M</t>
+  </si>
+  <si>
+    <t>FBA79114</t>
+  </si>
+  <si>
+    <t>B0CCV74CL7</t>
+  </si>
+  <si>
     <t>FBA79116</t>
   </si>
   <si>
-    <t>B07WLWN2ZT</t>
-  </si>
-  <si>
-    <t>B0BTCXQQ6M</t>
-  </si>
-  <si>
     <t>B0BYHHSLPC</t>
   </si>
   <si>
+    <t>FBA79576</t>
+  </si>
+  <si>
+    <t>B0BRCR2QQ7</t>
+  </si>
+  <si>
+    <t>FBA79586</t>
+  </si>
+  <si>
+    <t>B0CH9JR3HL</t>
+  </si>
+  <si>
+    <t>FBA79574</t>
+  </si>
+  <si>
+    <t>B0B4WTHLX5</t>
+  </si>
+  <si>
+    <t>FBA79585</t>
+  </si>
+  <si>
+    <t>B0CFKHCQ8W</t>
+  </si>
+  <si>
+    <t>FBA79697</t>
+  </si>
+  <si>
+    <t>B0CQX4K9P5</t>
+  </si>
+  <si>
+    <t>FBA79696</t>
+  </si>
+  <si>
+    <t>B0CQX3VB1R</t>
+  </si>
+  <si>
     <t>Tonor</t>
   </si>
   <si>
-    <t>B2B - AMPM</t>
-  </si>
-  <si>
     <t>TC-777</t>
   </si>
   <si>
+    <t>T30</t>
+  </si>
+  <si>
+    <t>TC30</t>
+  </si>
+  <si>
+    <t>TC-2030</t>
+  </si>
+  <si>
+    <t>TC40</t>
+  </si>
+  <si>
+    <t>TC40S</t>
+  </si>
+  <si>
+    <t>S20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TD510	</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC310	</t>
   </si>
   <si>
+    <t>TC310+</t>
+  </si>
+  <si>
     <t xml:space="preserve">TC-777 PRO	</t>
   </si>
   <si>
-    <t>FBA77114</t>
-  </si>
-  <si>
-    <t>B07TSN2H9D</t>
-  </si>
-  <si>
-    <t>TC-2030</t>
-  </si>
-  <si>
-    <t>Open Order</t>
-  </si>
-  <si>
-    <t>FBA79260</t>
-  </si>
-  <si>
-    <t>B07GVGMW59</t>
-  </si>
-  <si>
-    <t>FBA77105</t>
-  </si>
-  <si>
-    <t>B089FVQD3Z</t>
-  </si>
-  <si>
-    <t>FBA77111</t>
-  </si>
-  <si>
-    <t>B08CVP2HXP</t>
-  </si>
-  <si>
-    <t>FBA77115</t>
-  </si>
-  <si>
-    <t>B08V1JS3NY</t>
-  </si>
-  <si>
-    <t>FBA77116</t>
-  </si>
-  <si>
-    <t>B0BBL47VR5</t>
-  </si>
-  <si>
-    <t>FBA77117</t>
-  </si>
-  <si>
-    <t>B078WNW4YW</t>
-  </si>
-  <si>
-    <t>FBA77113</t>
-  </si>
-  <si>
-    <t>B01ISNU3X4</t>
-  </si>
-  <si>
-    <t>FBA77103</t>
-  </si>
-  <si>
-    <t>B09Z5Q194D</t>
-  </si>
-  <si>
-    <t>FBA79111</t>
-  </si>
-  <si>
-    <t>B0BRKFP94K</t>
-  </si>
-  <si>
-    <t>FBA79114</t>
-  </si>
-  <si>
-    <t>B0CCV74CL7</t>
-  </si>
-  <si>
-    <t>FBA79576</t>
-  </si>
-  <si>
-    <t>B0BRCR2QQ7</t>
-  </si>
-  <si>
-    <t>FBA79577</t>
-  </si>
-  <si>
-    <t>B0CSCT63BL</t>
-  </si>
-  <si>
-    <t>FBA79586</t>
-  </si>
-  <si>
-    <t>B0CH9JR3HL</t>
-  </si>
-  <si>
-    <t>FBA79574</t>
-  </si>
-  <si>
-    <t>B0B4WTHLX5</t>
-  </si>
-  <si>
-    <t>FBA79585</t>
-  </si>
-  <si>
-    <t>B0CFKHCQ8W</t>
-  </si>
-  <si>
-    <t>FBA79697</t>
-  </si>
-  <si>
-    <t>B0CQX4K9P5</t>
-  </si>
-  <si>
-    <t>FBA79696</t>
-  </si>
-  <si>
-    <t>B0CQX3VB1R</t>
-  </si>
-  <si>
-    <t>G11</t>
-  </si>
-  <si>
-    <t>T30</t>
-  </si>
-  <si>
-    <t>TC30</t>
-  </si>
-  <si>
-    <t>TC40</t>
-  </si>
-  <si>
-    <t>TC40S</t>
-  </si>
-  <si>
-    <t>S20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-K1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-ORCA001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TD510	</t>
-  </si>
-  <si>
-    <t>TC310+</t>
-  </si>
-  <si>
     <t>TC30S+</t>
   </si>
   <si>
-    <t>TM310</t>
-  </si>
-  <si>
     <t>TRL-20</t>
   </si>
   <si>
@@ -275,7 +252,10 @@
     <t>TD310+</t>
   </si>
   <si>
-    <t>AMPM</t>
+    <t>K1</t>
+  </si>
+  <si>
+    <t>ORCA001</t>
   </si>
 </sst>
 </file>
@@ -421,10 +401,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -873,7 +853,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -930,63 +910,63 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="I2" s="3">
+        <v>271</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="5">
-        <v>2</v>
-      </c>
-      <c r="J2" s="1" t="s">
+      <c r="C3" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="3">
+        <v>3</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="5">
-        <v>4</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="5">
-        <v>2</v>
+      <c r="C4" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="3">
+        <v>46</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -997,36 +977,36 @@
         <v>24</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="11">
-        <v>80</v>
-      </c>
-      <c r="J5" s="8" t="s">
-        <v>26</v>
+        <v>53</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="I5" s="3">
+        <v>6</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>20</v>
+        <v>53</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="I6" s="3">
-        <v>285</v>
+        <v>50</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1037,16 +1017,16 @@
         <v>28</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>61</v>
+        <v>53</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>60</v>
       </c>
       <c r="I7" s="3">
-        <v>5</v>
+        <v>114</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1057,16 +1037,16 @@
         <v>30</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>62</v>
+        <v>53</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="I8" s="3">
-        <v>5</v>
+        <v>393</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1077,16 +1057,16 @@
         <v>32</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>63</v>
+        <v>53</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>72</v>
       </c>
       <c r="I9" s="3">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1097,344 +1077,284 @@
         <v>34</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>64</v>
+        <v>53</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="I10" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>65</v>
+        <v>53</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="I11" s="3">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="3">
         <v>38</v>
       </c>
-      <c r="C12" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="I12" s="3">
-        <v>115</v>
-      </c>
       <c r="J12" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>67</v>
+        <v>53</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>65</v>
       </c>
       <c r="I13" s="3">
-        <v>473</v>
+        <v>8</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>68</v>
+        <v>53</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>66</v>
       </c>
       <c r="I14" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>69</v>
+        <v>53</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>67</v>
       </c>
       <c r="I15" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>21</v>
+        <v>53</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="I16" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>70</v>
+        <v>53</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>69</v>
       </c>
       <c r="I17" s="3">
-        <v>73</v>
+        <v>233</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>22</v>
+        <v>53</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>70</v>
       </c>
       <c r="I18" s="3">
-        <v>71</v>
+        <v>249</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>78</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="I19" s="3">
-        <v>8</v>
+      <c r="A19" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I19" s="5">
+        <v>2</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="A20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I20" s="5">
         <v>4</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="I21" s="3">
-        <v>5</v>
+      <c r="A21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="I21" s="5">
+        <v>2</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="I22" s="3">
-        <v>26</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="I23" s="3">
-        <v>7</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="I24" s="3">
-        <v>280</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I25" s="3">
-        <v>257</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>78</v>
+      <c r="I22" s="12">
+        <v>80</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A5">
-    <cfRule type="duplicateValues" dxfId="10" priority="2700"/>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="duplicateValues" dxfId="10" priority="2917"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2918"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="9" priority="2480"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="2670"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="8" priority="2691"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="2692" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="2881"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2882" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="6" priority="2478"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="2479" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2668"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2669" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="4" priority="2476"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2477" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2666"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2667" stopIfTrue="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A16:A17">
-    <cfRule type="duplicateValues" dxfId="2" priority="2704"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="2705"/>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="1" priority="2920"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A6:A25">
-    <cfRule type="duplicateValues" dxfId="0" priority="2712"/>
+  <conditionalFormatting sqref="A2:A18">
+    <cfRule type="duplicateValues" dxfId="0" priority="2923"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -504,7 +504,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -576,7 +576,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -712,7 +712,8 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t xml:space="preserve">
+K1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -720,7 +721,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>393</v>
+        <v>297</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -748,7 +749,8 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ORCA001</t>
+          <t xml:space="preserve">
+ORCA001</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -792,7 +794,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -828,7 +830,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -864,7 +866,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1044,7 +1046,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1080,7 +1082,7 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1120,7 +1122,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1156,7 +1158,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1192,7 +1194,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>B2B - AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,7 +576,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -712,8 +712,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-K1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -721,7 +720,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>297</v>
+        <v>206</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -749,8 +748,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">
-ORCA001</t>
+          <t>ORCA001</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -830,7 +828,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -866,7 +864,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -902,7 +900,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -974,7 +972,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -987,12 +985,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>FBA79585</t>
+          <t>FBA79697</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B0CQX4K9P5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1002,7 +1000,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>T20LP</t>
+          <t>TD310</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1010,7 +1008,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>194</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1023,12 +1021,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>FBA79697</t>
+          <t>FBA79696</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>B0CQX4K9P5</t>
+          <t>B0CQX3VB1R</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1038,7 +1036,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>TD310</t>
+          <t>TD310+</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1046,7 +1044,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1059,12 +1057,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>FBA79696</t>
+          <t>FBA79113</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>B0CQX3VB1R</t>
+          <t>B0BTCXQQ6M</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1074,7 +1072,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>TD310+</t>
+          <t xml:space="preserve">TC310	</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -1082,11 +1080,11 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="n">
-        <v>240</v>
+        <v>2</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>AMPM</t>
+          <t>B2B-AMPM</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1095,12 +1093,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>FBA79113</t>
+          <t>FBA79116</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>B0BTCXQQ6M</t>
+          <t>B0BYHHSLPC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1110,7 +1108,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC310	</t>
+          <t xml:space="preserve">TC-777 PRO	</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -1118,7 +1116,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1131,12 +1129,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FBA79116</t>
+          <t>FBA77101</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B07WLWN2ZT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1146,7 +1144,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-777 PRO	</t>
+          <t>TC-777</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -1154,7 +1152,7 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1167,12 +1165,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FBA77101</t>
+          <t>FBA77114</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B07WLWN2ZT</t>
+          <t>B07TSN2H9D</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1182,7 +1180,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TC-777</t>
+          <t>TC-2030</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1190,11 +1188,11 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>B2B-AMPM</t>
+          <t>Open Order</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1203,12 +1201,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FBA77114</t>
+          <t>FBA77106</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B07TSN2H9D</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1218,7 +1216,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TC-2030</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1226,7 +1224,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1239,12 +1237,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBA77106</t>
+          <t>FBA79260</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1254,7 +1252,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>G11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1262,7 +1260,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>104</v>
+        <v>360</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1271,42 +1269,6 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>FBA79260</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>B07GVGMW59</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Tonor</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>G11</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="n">
-        <v>360</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Open Order</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FBA77114</t>
+          <t>FBA77110</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B07TSN2H9D</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TC-2030</t>
+          <t>TM20</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1188,7 +1188,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FBA77106</t>
+          <t>FBA77114</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B07TSN2H9D</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>TC-2030</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1224,7 +1224,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1237,12 +1237,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBA79260</t>
+          <t>FBA77106</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>G11</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>360</v>
+        <v>104</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1269,6 +1269,78 @@
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FBA79260</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>B07GVGMW59</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>G11</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>360</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FBA79585</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>B0CFKHCQ8W</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>T20LP</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>100</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -576,7 +576,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -684,7 +684,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -720,7 +720,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -841,12 +841,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FBA79116</t>
+          <t>FBA79576</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B0BYHHSLPC</t>
+          <t>B0BRCR2QQ7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">TC-777 PRO	</t>
+          <t>TC30S+</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -864,7 +864,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -877,12 +877,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>FBA79576</t>
+          <t>FBA79586</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>B0BRCR2QQ7</t>
+          <t>B0CH9JR3HL</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TC30S+</t>
+          <t>TRL-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -913,12 +913,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>FBA79586</t>
+          <t>FBA79574</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>B0CH9JR3HL</t>
+          <t>B0B4WTHLX5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>TRL-20</t>
+          <t>TC30S</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -936,7 +936,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>FBA79574</t>
+          <t>FBA79585</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B0B4WTHLX5</t>
+          <t>B0CFKHCQ8W</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TC30S</t>
+          <t>T20LP</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -972,7 +972,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>194</v>
+        <v>130</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1044,7 +1044,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="n">
-        <v>210</v>
+        <v>175</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>

--- a/data/input/Inventory_snapshot_tonor.xlsx
+++ b/data/input/Inventory_snapshot_tonor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L25"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1165,12 +1165,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FBA77110</t>
+          <t>FBA77113</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>B08NDB5NWP</t>
+          <t>B01ISNU3X4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>TM20</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -1188,7 +1188,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>300</v>
+        <v>1026</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1201,12 +1201,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FBA77114</t>
+          <t>FBA77110</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>B07TSN2H9D</t>
+          <t>B08NDB5NWP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>TC-2030</t>
+          <t>TM20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -1224,7 +1224,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1237,12 +1237,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FBA77106</t>
+          <t>FBA77114</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B082W4B7SX</t>
+          <t>B07TSN2H9D</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>TC-2030</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1273,12 +1273,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>FBA79260</t>
+          <t>FBA77106</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B07GVGMW59</t>
+          <t>B082W4B7SX</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>G11</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -1296,7 +1296,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="n">
-        <v>360</v>
+        <v>104</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1309,12 +1309,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>FBA79585</t>
+          <t>FBA79260</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B0CFKHCQ8W</t>
+          <t>B07GVGMW59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>T20LP</t>
+          <t>G11</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -1332,7 +1332,7 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="n">
-        <v>100</v>
+        <v>360</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1341,6 +1341,42 @@
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FBA79585</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>B0CFKHCQ8W</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Tonor</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>T20LP</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>100</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Open Order</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
